--- a/tables and figures/results/thesis_tables.xlsx
+++ b/tables and figures/results/thesis_tables.xlsx
@@ -11,21 +11,20 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table-format" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_1" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_2" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_3a" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_3b" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_4a" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_5" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_6" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_7" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_8" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_9" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_10" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_11" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_5_1" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_5_2" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_5_3" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_5_4" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dual_track_policy" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_3" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_4" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_5" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_6" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_7" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_8" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_9" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_10" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_11" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_5_1" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_5_2" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_5_3" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_5_4" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dual_track_policy" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -39,7 +38,7 @@
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -97,6 +96,31 @@
       <name val="Calibri"/>
       <i val="1"/>
       <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="000000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -158,7 +182,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -265,6 +289,16 @@
     <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -630,1648 +664,434 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
-    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="92" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="73" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>THESIS MASTER EMPIRICAL TABLES CATALOG (thesis_tables.xlsx)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Evaluating Predictive Techniques to Model Stochastic Airport Passenger Flow | MSAA / Gleich 700B | Leila Gleich</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Interactive Table Index: Click any Sheet Name or Table ID to navigate directly to that table. Every worksheet includes a '⬅ Return to Table of Contents' link in Cell A1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="10" customHeight="1"/>
-    <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Table ID</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Sheet Tab (Click to Jump)</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Official Manuscript Table Title</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Manuscript Chapter</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Dimensions</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Operational Scope &amp; Core Finding</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>Evaluation Dimension</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Template</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>table-format</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>APA Style Reference Template (Demographic Characteristics)</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>Results Appendix</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>8 rows x 4 cols</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>APA 7th Edition Sample Table Template (Clean boundary rules, no filters, no fill)</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>Formatting Specification</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="40" t="inlineStr">
+        <is>
+          <t>MASTER THESIS RESULTS &amp; FINDINGS TABLES</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="41" t="inlineStr">
+        <is>
+          <t>Evaluating Predictive Techniques to Model Stochastic Airport Passenger Flow | Gleich 700B</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="42" t="inlineStr">
+        <is>
+          <t>Table Number</t>
+        </is>
+      </c>
+      <c r="B4" s="42" t="inlineStr">
+        <is>
+          <t>Sheet Name</t>
+        </is>
+      </c>
+      <c r="C4" s="42" t="inlineStr">
+        <is>
+          <t>Table Title</t>
+        </is>
+      </c>
+      <c r="D4" s="42" t="inlineStr">
+        <is>
+          <t>Chapter / Operational Scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="43" t="inlineStr">
         <is>
           <t>Table 4.1</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B5" s="44" t="inlineStr">
         <is>
           <t>table_4_1</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>Master Post-ETL Multi-Source Data Foundation Census (Full Candidate Commercial Network)</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>Chapter 4: Results</t>
-        </is>
-      </c>
-      <c r="E7" s="10" t="inlineStr">
-        <is>
-          <t>5 rows x 6 cols</t>
-        </is>
-      </c>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t>Census of 4 conformed federal feeds (TSA FOIA, BTS OTP, BTS T-100, BTS DB1B) covering 42,062,039 records</t>
-        </is>
-      </c>
-      <c r="G7" s="10" t="inlineStr">
-        <is>
-          <t>Data Foundation &amp; ETL Census</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="C5" s="45" t="inlineStr">
+        <is>
+          <t>Master Post-ETL Multi-Source Data Foundation Census</t>
+        </is>
+      </c>
+      <c r="D5" s="46" t="inlineStr">
+        <is>
+          <t>Chapter IV: Findings (Data Foundation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="43" t="inlineStr">
         <is>
           <t>Table 4.2</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B6" s="44" t="inlineStr">
         <is>
           <t>table_4_2</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>Post-ETL Master Summary Descriptive Statistics (Top 25 Cleaned Data Warehouse)</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>Chapter 4: Results</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="inlineStr">
-        <is>
-          <t>11 rows x 11 cols</t>
-        </is>
-      </c>
-      <c r="F8" s="9" t="inlineStr">
-        <is>
-          <t>Master descriptive moments (mean, std dev, median, IQR, skewness, kurtosis) across all operational variables</t>
-        </is>
-      </c>
-      <c r="G8" s="10" t="inlineStr">
-        <is>
-          <t>Descriptive Statistics</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>Table 4.3a</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>table_4_3a</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>Post-Pandemic Temporal Demarcation Evaluation Across the Top 25 Network</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>Chapter 4: Results</t>
-        </is>
-      </c>
-      <c r="E9" s="10" t="inlineStr">
-        <is>
-          <t>8 rows x 3 cols</t>
-        </is>
-      </c>
-      <c r="F9" s="9" t="inlineStr">
-        <is>
-          <t>Comparison of Candidate A (Mature Post-Pandemic) and Candidate B (Early Post-Mask Regime; Selected, 44 months)</t>
-        </is>
-      </c>
-      <c r="G9" s="10" t="inlineStr">
-        <is>
-          <t>Temporal Demarcation</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>Table 4.3b</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>table_4_3b</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>Master Annual Seasonal Volatility Regimes Summary (Top 25 Airfields)</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>Chapter 4: Results</t>
-        </is>
-      </c>
-      <c r="E10" s="10" t="inlineStr">
-        <is>
-          <t>4 rows x 11 cols</t>
-        </is>
-      </c>
-      <c r="F10" s="9" t="inlineStr">
-        <is>
-          <t>Annual seasonal volatility regimes (Off-Peak, Mid-Peak, Peak, Holiday) across 1,341 post-demarcation days</t>
-        </is>
-      </c>
-      <c r="G10" s="10" t="inlineStr">
-        <is>
-          <t>Seasonality &amp; Volatility Regimes</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Table 4.4a</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>table_4_4a</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>Day-of-Week Volatility Dynamics and Operational Archetypes (Top 25 Airfields)</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>Chapter 4: Results</t>
-        </is>
-      </c>
-      <c r="E11" s="10" t="inlineStr">
-        <is>
-          <t>7 rows x 10 cols</t>
-        </is>
-      </c>
-      <c r="F11" s="9" t="inlineStr">
-        <is>
-          <t>Weekly cyclical dynamics and operational archetypes across Monday through Sunday</t>
-        </is>
-      </c>
-      <c r="G11" s="10" t="inlineStr">
-        <is>
-          <t>Weekly Cyclical Dynamics</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="C6" s="45" t="inlineStr">
+        <is>
+          <t>Post-ETL Master Summary Descriptive Statistics</t>
+        </is>
+      </c>
+      <c r="D6" s="46" t="inlineStr">
+        <is>
+          <t>Chapter IV: Findings (Descriptive Scale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="43" t="inlineStr">
+        <is>
+          <t>Table 4.3</t>
+        </is>
+      </c>
+      <c r="B7" s="44" t="inlineStr">
+        <is>
+          <t>table_4_3</t>
+        </is>
+      </c>
+      <c r="C7" s="45" t="inlineStr">
+        <is>
+          <t>Master Annual Seasonal Volatility Regimes Summary</t>
+        </is>
+      </c>
+      <c r="D7" s="46" t="inlineStr">
+        <is>
+          <t>Chapter IV: Findings (Annual Regimes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="43" t="inlineStr">
+        <is>
+          <t>Table 4.4</t>
+        </is>
+      </c>
+      <c r="B8" s="44" t="inlineStr">
+        <is>
+          <t>table_4_4</t>
+        </is>
+      </c>
+      <c r="C8" s="45" t="inlineStr">
+        <is>
+          <t>Master Day-of-Week Operational Volatility Regimes</t>
+        </is>
+      </c>
+      <c r="D8" s="46" t="inlineStr">
+        <is>
+          <t>Chapter IV: Findings (DOW Archetypes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="43" t="inlineStr">
         <is>
           <t>Table 4.5</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B9" s="44" t="inlineStr">
         <is>
           <t>table_4_5</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>Master Cross-Dataset Econometric Relationships (Top 25 Airfields)</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>Chapter 4: Results</t>
-        </is>
-      </c>
-      <c r="E12" s="10" t="inlineStr">
-        <is>
-          <t>12 rows x 9 cols</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="inlineStr">
-        <is>
-          <t>Econometric coupling between TSA checkpoint volumes and BTS OTP delays/capacity across 12 operational dimensions</t>
-        </is>
-      </c>
-      <c r="G12" s="10" t="inlineStr">
-        <is>
-          <t>Econometric Coupling</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="C9" s="45" t="inlineStr">
+        <is>
+          <t>Master Cross-Dataset Econometric Relationships</t>
+        </is>
+      </c>
+      <c r="D9" s="46" t="inlineStr">
+        <is>
+          <t>Chapter IV: Findings (Econometric Coupling)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="43" t="inlineStr">
         <is>
           <t>Table 4.6</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B10" s="44" t="inlineStr">
         <is>
           <t>table_4_6</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>The Nine-Airport Experimental Cohort Factorial Specification</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>Chapter 4: Results</t>
-        </is>
-      </c>
-      <c r="E13" s="10" t="inlineStr">
-        <is>
-          <t>9 rows x 7 cols</t>
-        </is>
-      </c>
-      <c r="F13" s="9" t="inlineStr">
-        <is>
-          <t>Balanced 4x4 factorial design across 12 carrier-exclusive complexes at 9 hubs (BOS, DFW, DTW, EWR, IAH, LAX, LGA, ORD, PHL)</t>
-        </is>
-      </c>
-      <c r="G13" s="10" t="inlineStr">
-        <is>
-          <t>Experimental Cohort Design</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="C10" s="45" t="inlineStr">
+        <is>
+          <t>Nine-Airport Experimental Cohort Factorial Specification</t>
+        </is>
+      </c>
+      <c r="D10" s="46" t="inlineStr">
+        <is>
+          <t>Chapter IV: Findings (4x4 Matrix)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="43" t="inlineStr">
         <is>
           <t>Table 4.7</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B11" s="44" t="inlineStr">
         <is>
           <t>table_4_7</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>Summary Descriptive Statistics: Nine-Airport Experimental Cohort Versus Top 25 Universe</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>Chapter 4: Results</t>
-        </is>
-      </c>
-      <c r="E14" s="10" t="inlineStr">
-        <is>
-          <t>16 rows x 10 cols</t>
-        </is>
-      </c>
-      <c r="F14" s="9" t="inlineStr">
-        <is>
-          <t>Formal comparison proving sample representativeness of the 9-airport experimental cohort against the Top 25 universe</t>
-        </is>
-      </c>
-      <c r="G14" s="10" t="inlineStr">
-        <is>
-          <t>Sample Representativeness</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="C11" s="45" t="inlineStr">
+        <is>
+          <t>Summary Descriptive Statistics: Nine-Airport Cohort vs. Top 25</t>
+        </is>
+      </c>
+      <c r="D11" s="46" t="inlineStr">
+        <is>
+          <t>Chapter IV: Findings (Cohort Contrast)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="43" t="inlineStr">
         <is>
           <t>Table 4.8</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B12" s="44" t="inlineStr">
         <is>
           <t>table_4_8</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>Day-of-Week Mean Daily Passenger Throughput Across the Nine Selected Airports</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr">
-        <is>
-          <t>Chapter 4: Results</t>
-        </is>
-      </c>
-      <c r="E15" s="10" t="inlineStr">
-        <is>
-          <t>9 rows x 12 cols</t>
-        </is>
-      </c>
-      <c r="F15" s="9" t="inlineStr">
-        <is>
-          <t>Local airport DOW profiles, weekly peak/trough days, and Peak/Trough ratios (highlighting LGA corporate profile = 2.30)</t>
-        </is>
-      </c>
-      <c r="G15" s="10" t="inlineStr">
-        <is>
-          <t>Local Airport Demand Profiles</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="C12" s="45" t="inlineStr">
+        <is>
+          <t>Day-of-Week Mean Daily Passenger Throughput Across Nine Airports</t>
+        </is>
+      </c>
+      <c r="D12" s="46" t="inlineStr">
+        <is>
+          <t>Chapter IV: Findings (Local DOW Scale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="43" t="inlineStr">
         <is>
           <t>Table 4.9</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B13" s="44" t="inlineStr">
         <is>
           <t>table_4_9</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>Empirical Lead-Lag Transfer Dynamics (Scheduled Flights Versus Checkpoint Demand)</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>Chapter 4: Results</t>
-        </is>
-      </c>
-      <c r="E16" s="10" t="inlineStr">
-        <is>
-          <t>7 rows x 5 cols</t>
-        </is>
-      </c>
-      <c r="F16" s="9" t="inlineStr">
-        <is>
-          <t>Asymmetric correlation and explanatory power across Lag t-1, Same-Hour t, Lead t+1, t+2, t+3, and convolved kernels</t>
-        </is>
-      </c>
-      <c r="G16" s="10" t="inlineStr">
-        <is>
-          <t>Lead-Lag Show-Up Dynamics</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="C13" s="45" t="inlineStr">
+        <is>
+          <t>Empirical Lead-Lag Transfer Dynamics</t>
+        </is>
+      </c>
+      <c r="D13" s="46" t="inlineStr">
+        <is>
+          <t>Chapter IV: Findings (Show-Up Convolution)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="43" t="inlineStr">
         <is>
           <t>Table 4.10</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B14" s="44" t="inlineStr">
         <is>
           <t>table_4_10</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>Master Model Benchmark Matrix for TSA Throughput Volatility (2025 Full-Year Out-of-Time Holdout)</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>Chapter 4: Results</t>
-        </is>
-      </c>
-      <c r="E17" s="10" t="inlineStr">
-        <is>
-          <t>4 rows x 10 cols</t>
-        </is>
-      </c>
-      <c r="F17" s="9" t="inlineStr">
-        <is>
-          <t>Master benchmark matrix across candidate predictive models and baseline control on 72,053 holdout observations</t>
-        </is>
-      </c>
-      <c r="G17" s="10" t="inlineStr">
-        <is>
-          <t>Model Evaluation (Holdout)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="C14" s="45" t="inlineStr">
+        <is>
+          <t>Master Model Benchmark Matrix (2025 Full-Year Holdout)</t>
+        </is>
+      </c>
+      <c r="D14" s="46" t="inlineStr">
+        <is>
+          <t>Chapter IV: Findings (Model Accuracy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="43" t="inlineStr">
         <is>
           <t>Table 4.11</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B15" s="44" t="inlineStr">
         <is>
           <t>table_4_11</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>Master Multi-Pillar Hypothesis Evaluation Matrix Across the Four Models (Throughput Volatility)</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="inlineStr">
-        <is>
-          <t>Chapter 4: Results</t>
-        </is>
-      </c>
-      <c r="E18" s="10" t="inlineStr">
-        <is>
-          <t>11 rows x 9 cols</t>
-        </is>
-      </c>
-      <c r="F18" s="9" t="inlineStr">
-        <is>
-          <t>Formal empirical hypothesis test matrix across Robustness, Resilience, and Generalizability with explicit targets</t>
-        </is>
-      </c>
-      <c r="G18" s="10" t="inlineStr">
-        <is>
-          <t>Hypothesis Testing (H1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="C15" s="45" t="inlineStr">
+        <is>
+          <t>Master Multi-Pillar Hypothesis Evaluation Matrix</t>
+        </is>
+      </c>
+      <c r="D15" s="46" t="inlineStr">
+        <is>
+          <t>Chapter IV: Findings (Hypothesis 1 Test)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="43" t="inlineStr">
         <is>
           <t>Table 5.1</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B16" s="44" t="inlineStr">
         <is>
           <t>table_5_1</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>Evaluation Dimension 1: Routine Operational Accuracy Across the Candidate Models</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>Chapter 5: Discussion</t>
-        </is>
-      </c>
-      <c r="E19" s="10" t="inlineStr">
-        <is>
-          <t>4 rows x 8 cols</t>
-        </is>
-      </c>
-      <c r="F19" s="9" t="inlineStr">
-        <is>
-          <t>Robustness evaluation under nominal flight conditions (RMSE, MASE, stated target MASE &lt; 0.70, Diebold-Mariano test)</t>
-        </is>
-      </c>
-      <c r="G19" s="10" t="inlineStr">
-        <is>
-          <t>Dimension 1: Robustness</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="C16" s="45" t="inlineStr">
+        <is>
+          <t>Evaluation Dimension 1: Routine Operational Accuracy (Robustness)</t>
+        </is>
+      </c>
+      <c r="D16" s="46" t="inlineStr">
+        <is>
+          <t>Chapter V: Analysis (Dimension 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="43" t="inlineStr">
         <is>
           <t>Table 5.2</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B17" s="44" t="inlineStr">
         <is>
           <t>table_5_2</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>Evaluation Dimension 2: Resilience and Shock Performance Under Severe Operational Disruption</t>
-        </is>
-      </c>
-      <c r="D20" s="10" t="inlineStr">
-        <is>
-          <t>Chapter 5: Discussion</t>
-        </is>
-      </c>
-      <c r="E20" s="10" t="inlineStr">
-        <is>
-          <t>4 rows x 9 cols</t>
-        </is>
-      </c>
-      <c r="F20" s="9" t="inlineStr">
-        <is>
-          <t>Resilience evaluation under severe weather ground stops and delay programs (RMSE, MASE, R_MASE ≈ 1.00, TTR &lt; 4.0h)</t>
-        </is>
-      </c>
-      <c r="G20" s="10" t="inlineStr">
-        <is>
-          <t>Dimension 2: Resilience</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="C17" s="45" t="inlineStr">
+        <is>
+          <t>Evaluation Dimension 2: Resilience Under Disruption (IROPS Regimes)</t>
+        </is>
+      </c>
+      <c r="D17" s="46" t="inlineStr">
+        <is>
+          <t>Chapter V: Analysis (Dimension 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="43" t="inlineStr">
         <is>
           <t>Table 5.3</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B18" s="44" t="inlineStr">
         <is>
           <t>table_5_3</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>Evaluation Dimension 3: Generalizability and Cross-Airport Transfer Performance</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>Chapter 5: Discussion</t>
-        </is>
-      </c>
-      <c r="E21" s="10" t="inlineStr">
-        <is>
-          <t>4 rows x 9 cols</t>
-        </is>
-      </c>
-      <c r="F21" s="9" t="inlineStr">
-        <is>
-          <t>Zero-shot spatial transfer evaluation from EWR to LGA without retraining (RMSE, RTR = 1.00, Delta MASE &lt;= 10.0%)</t>
-        </is>
-      </c>
-      <c r="G21" s="10" t="inlineStr">
-        <is>
-          <t>Dimension 3: Generalizability</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="C18" s="45" t="inlineStr">
+        <is>
+          <t>Evaluation Dimension 3: Generalizability Across Facilities (Zero-Shot)</t>
+        </is>
+      </c>
+      <c r="D18" s="46" t="inlineStr">
+        <is>
+          <t>Chapter V: Analysis (Dimension 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="43" t="inlineStr">
         <is>
           <t>Table 5.4</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B19" s="44" t="inlineStr">
         <is>
           <t>table_5_4</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>Master Asymmetric Trade-Off Matrix Across the Candidate Models</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>Chapter 5: Discussion</t>
-        </is>
-      </c>
-      <c r="E22" s="10" t="inlineStr">
-        <is>
-          <t>3 rows x 7 cols</t>
-        </is>
-      </c>
-      <c r="F22" s="9" t="inlineStr">
-        <is>
-          <t>Synthesis of architectural trade-offs demonstrating asymmetric performance strengths across the candidate models</t>
-        </is>
-      </c>
-      <c r="G22" s="10" t="inlineStr">
-        <is>
-          <t>Architectural Synthesis</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>Policy 5.1</t>
-        </is>
-      </c>
-      <c r="B23" s="12" t="inlineStr">
+      <c r="C19" s="45" t="inlineStr">
+        <is>
+          <t>Master Asymmetric Trade-Off Matrix (H1 Synthesis)</t>
+        </is>
+      </c>
+      <c r="D19" s="46" t="inlineStr">
+        <is>
+          <t>Chapter V: Analysis (Master Trade-Offs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="43" t="inlineStr">
+        <is>
+          <t>Dual-Track Policy</t>
+        </is>
+      </c>
+      <c r="B20" s="44" t="inlineStr">
         <is>
           <t>dual_track_policy</t>
         </is>
       </c>
-      <c r="C23" s="13" t="inlineStr">
-        <is>
-          <t>Dual-Track Operational Model Selection Policy</t>
-        </is>
-      </c>
-      <c r="D23" s="14" t="inlineStr">
-        <is>
-          <t>Chapter 5: Discussion</t>
-        </is>
-      </c>
-      <c r="E23" s="14" t="inlineStr">
-        <is>
-          <t>2 rows x 6 cols</t>
-        </is>
-      </c>
-      <c r="F23" s="13" t="inlineStr">
-        <is>
-          <t>Gated operational deployment rules for Gate 1 (Routine Flow Track -&gt; Model 2) and Gate 2 (Tactical Shock Track -&gt; Model 3)</t>
-        </is>
-      </c>
-      <c r="G23" s="14" t="inlineStr">
-        <is>
-          <t>Deployment Policy Matrix</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>Note. Master empirical table catalog conformed across Chapter IV (Results) and Chapter V (Discussion). Formatted according to APA Style (7th ed.) with horizontal boundary rules and no filter dropdowns.</t>
-        </is>
-      </c>
+      <c r="C20" s="45" t="inlineStr">
+        <is>
+          <t>Dual-Track Operational Decision Playbook for Checkpoint Managers</t>
+        </is>
+      </c>
+      <c r="D20" s="46" t="inlineStr">
+        <is>
+          <t>Chapter V: Analysis (Operational Playbook)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="47" t="n"/>
+      <c r="B21" s="47" t="n"/>
+      <c r="C21" s="47" t="n"/>
+      <c r="D21" s="47" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="27" customWidth="1" min="7" max="7"/>
-    <col width="27" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="23" t="inlineStr">
-        <is>
-          <t>⬅ Return to Table of Contents</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="24" t="inlineStr">
-        <is>
-          <t>Table 4.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="25" t="inlineStr">
-        <is>
-          <t>Summary Descriptive Statistics: Nine-Airport Experimental Cohort Versus Top 25 Universe</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="10" customHeight="1"/>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Metric Category</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Operational Metric</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>9-Airport Mean</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>9-Airport Std Dev</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>9-Airport Median</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>9-Airport Min (Airport)</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>9-Airport Max (Airport)</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>Top 25 Mean</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>Delta (%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>BTS OTP Operations</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>Scheduled Domestic Flights</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>flights</t>
-        </is>
-      </c>
-      <c r="D6" s="26" t="n">
-        <v>224576</v>
-      </c>
-      <c r="E6" s="26" t="n">
-        <v>78441</v>
-      </c>
-      <c r="F6" s="26" t="n">
-        <v>206024</v>
-      </c>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>138,372 (PHL)</t>
-        </is>
-      </c>
-      <c r="H6" s="9" t="inlineStr">
-        <is>
-          <t>360,571 (ORD)</t>
-        </is>
-      </c>
-      <c r="I6" s="26" t="n">
-        <v>192160</v>
-      </c>
-      <c r="J6" s="31" t="inlineStr">
-        <is>
-          <t>+16.9%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>BTS OTP Operations</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>Cancelled Flights</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>flights</t>
-        </is>
-      </c>
-      <c r="D7" s="26" t="n">
-        <v>3623</v>
-      </c>
-      <c r="E7" s="26" t="n">
-        <v>1599</v>
-      </c>
-      <c r="F7" s="26" t="n">
-        <v>2920</v>
-      </c>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>1,777 (DTW)</t>
-        </is>
-      </c>
-      <c r="H7" s="9" t="inlineStr">
-        <is>
-          <t>6,515 (DFW)</t>
-        </is>
-      </c>
-      <c r="I7" s="26" t="n">
-        <v>2738</v>
-      </c>
-      <c r="J7" s="31" t="inlineStr">
-        <is>
-          <t>+32.3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>BTS OTP Operations</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>Flight Cancellation Rate</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D8" s="31" t="inlineStr">
-        <is>
-          <t>1.63%</t>
-        </is>
-      </c>
-      <c r="E8" s="31" t="inlineStr">
-        <is>
-          <t>0.50%</t>
-        </is>
-      </c>
-      <c r="F8" s="31" t="inlineStr">
-        <is>
-          <t>1.47%</t>
-        </is>
-      </c>
-      <c r="G8" s="9" t="inlineStr">
-        <is>
-          <t>0.99% (LAX)</t>
-        </is>
-      </c>
-      <c r="H8" s="9" t="inlineStr">
-        <is>
-          <t>2.46% (LGA)</t>
-        </is>
-      </c>
-      <c r="I8" s="31" t="inlineStr">
-        <is>
-          <t>1.43%</t>
-        </is>
-      </c>
-      <c r="J8" s="31" t="inlineStr">
-        <is>
-          <t>+14.1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>BTS OTP Delays</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>Average Departure Delay</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>min</t>
-        </is>
-      </c>
-      <c r="D9" s="29" t="n">
-        <v>15.23</v>
-      </c>
-      <c r="E9" s="29" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="F9" s="29" t="n">
-        <v>15.65</v>
-      </c>
-      <c r="G9" s="9" t="inlineStr">
-        <is>
-          <t>11.55 (DTW)</t>
-        </is>
-      </c>
-      <c r="H9" s="9" t="inlineStr">
-        <is>
-          <t>19.85 (DFW)</t>
-        </is>
-      </c>
-      <c r="I9" s="29" t="n">
-        <v>14.21</v>
-      </c>
-      <c r="J9" s="31" t="inlineStr">
-        <is>
-          <t>+7.2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>BTS OTP Delays</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>Significant Delay Rate (&gt;= 15m)</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D10" s="31" t="inlineStr">
-        <is>
-          <t>21.42%</t>
-        </is>
-      </c>
-      <c r="E10" s="31" t="inlineStr">
-        <is>
-          <t>3.30%</t>
-        </is>
-      </c>
-      <c r="F10" s="31" t="inlineStr">
-        <is>
-          <t>20.14%</t>
-        </is>
-      </c>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>17.93% (LAX)</t>
-        </is>
-      </c>
-      <c r="H10" s="9" t="inlineStr">
-        <is>
-          <t>28.07% (DFW)</t>
-        </is>
-      </c>
-      <c r="I10" s="31" t="inlineStr">
-        <is>
-          <t>20.31%</t>
-        </is>
-      </c>
-      <c r="J10" s="31" t="inlineStr">
-        <is>
-          <t>+5.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>BTS OTP Delays</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>Runway Taxi-Out Queue Time</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>min</t>
-        </is>
-      </c>
-      <c r="D11" s="29" t="n">
-        <v>20.59</v>
-      </c>
-      <c r="E11" s="29" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="F11" s="29" t="n">
-        <v>20.35</v>
-      </c>
-      <c r="G11" s="9" t="inlineStr">
-        <is>
-          <t>16.96 (DTW)</t>
-        </is>
-      </c>
-      <c r="H11" s="9" t="inlineStr">
-        <is>
-          <t>24.67 (EWR)</t>
-        </is>
-      </c>
-      <c r="I11" s="29" t="n">
-        <v>19.69</v>
-      </c>
-      <c r="J11" s="31" t="inlineStr">
-        <is>
-          <t>+4.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>TSA Checkpoint</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>Total Passenger Throughput</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>pax</t>
-        </is>
-      </c>
-      <c r="D12" s="26" t="n">
-        <v>71145628</v>
-      </c>
-      <c r="E12" s="26" t="n">
-        <v>27465238</v>
-      </c>
-      <c r="F12" s="26" t="n">
-        <v>63720916</v>
-      </c>
-      <c r="G12" s="9" t="inlineStr">
-        <is>
-          <t>40,429,531 (PHL)</t>
-        </is>
-      </c>
-      <c r="H12" s="9" t="inlineStr">
-        <is>
-          <t>129,069,341 (LAX)</t>
-        </is>
-      </c>
-      <c r="I12" s="26" t="n">
-        <v>68495531</v>
-      </c>
-      <c r="J12" s="31" t="inlineStr">
-        <is>
-          <t>+3.9%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>TSA Checkpoint</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>Average Daily Passenger Count</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>pax/day</t>
-        </is>
-      </c>
-      <c r="D13" s="26" t="n">
-        <v>53075</v>
-      </c>
-      <c r="E13" s="26" t="n">
-        <v>20473</v>
-      </c>
-      <c r="F13" s="26" t="n">
-        <v>47553</v>
-      </c>
-      <c r="G13" s="9" t="inlineStr">
-        <is>
-          <t>30,171 (PHL)</t>
-        </is>
-      </c>
-      <c r="H13" s="9" t="inlineStr">
-        <is>
-          <t>96,249 (LAX)</t>
-        </is>
-      </c>
-      <c r="I13" s="26" t="n">
-        <v>51138</v>
-      </c>
-      <c r="J13" s="31" t="inlineStr">
-        <is>
-          <t>+3.8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>TSA Checkpoint</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>Average Hourly Passenger Count</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>pax/hr</t>
-        </is>
-      </c>
-      <c r="D14" s="29" t="n">
-        <v>418.53</v>
-      </c>
-      <c r="E14" s="29" t="n">
-        <v>157.02</v>
-      </c>
-      <c r="F14" s="29" t="n">
-        <v>388.4</v>
-      </c>
-      <c r="G14" s="9" t="inlineStr">
-        <is>
-          <t>239.60 (ORD)</t>
-        </is>
-      </c>
-      <c r="H14" s="9" t="inlineStr">
-        <is>
-          <t>662.40 (LGA)</t>
-        </is>
-      </c>
-      <c r="I14" s="29" t="n">
-        <v>540.34</v>
-      </c>
-      <c r="J14" s="31" t="inlineStr">
-        <is>
-          <t>-22.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>TSA Checkpoint</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>Peak Single-Hour Checkpoint Rush</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>pax/hr</t>
-        </is>
-      </c>
-      <c r="D15" s="26" t="n">
-        <v>2673</v>
-      </c>
-      <c r="E15" s="26" t="n">
-        <v>881</v>
-      </c>
-      <c r="F15" s="26" t="n">
-        <v>2654</v>
-      </c>
-      <c r="G15" s="9" t="inlineStr">
-        <is>
-          <t>1,385 (DTW)</t>
-        </is>
-      </c>
-      <c r="H15" s="9" t="inlineStr">
-        <is>
-          <t>4,020 (EWR)</t>
-        </is>
-      </c>
-      <c r="I15" s="26" t="n">
-        <v>2784</v>
-      </c>
-      <c r="J15" s="31" t="inlineStr">
-        <is>
-          <t>-4.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>TSA Checkpoint</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>Demand Volatility (CV_TSA)</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="D16" s="36" t="n">
-        <v>0.8728</v>
-      </c>
-      <c r="E16" s="36" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F16" s="36" t="n">
-        <v>0.9064</v>
-      </c>
-      <c r="G16" s="9" t="inlineStr">
-        <is>
-          <t>0.6488 (BOS)</t>
-        </is>
-      </c>
-      <c r="H16" s="9" t="inlineStr">
-        <is>
-          <t>1.1240 (LGA)</t>
-        </is>
-      </c>
-      <c r="I16" s="36" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="J16" s="31" t="inlineStr">
-        <is>
-          <t>+5.8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>BTS DB1B Surveys</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>Connecting Passenger Share</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D17" s="31" t="inlineStr">
-        <is>
-          <t>47.45%</t>
-        </is>
-      </c>
-      <c r="E17" s="31" t="inlineStr">
-        <is>
-          <t>10.98%</t>
-        </is>
-      </c>
-      <c r="F17" s="31" t="inlineStr">
-        <is>
-          <t>44.41%</t>
-        </is>
-      </c>
-      <c r="G17" s="9" t="inlineStr">
-        <is>
-          <t>33.58% (EWR)</t>
-        </is>
-      </c>
-      <c r="H17" s="9" t="inlineStr">
-        <is>
-          <t>66.32% (DFW)</t>
-        </is>
-      </c>
-      <c r="I17" s="31" t="inlineStr">
-        <is>
-          <t>51.39%</t>
-        </is>
-      </c>
-      <c r="J17" s="31" t="inlineStr">
-        <is>
-          <t>-7.7%</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>BTS DB1B Surveys</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>Local Originating Passenger Share</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D18" s="31" t="inlineStr">
-        <is>
-          <t>52.55%</t>
-        </is>
-      </c>
-      <c r="E18" s="31" t="inlineStr">
-        <is>
-          <t>10.98%</t>
-        </is>
-      </c>
-      <c r="F18" s="31" t="inlineStr">
-        <is>
-          <t>55.59%</t>
-        </is>
-      </c>
-      <c r="G18" s="9" t="inlineStr">
-        <is>
-          <t>33.68% (DFW)</t>
-        </is>
-      </c>
-      <c r="H18" s="9" t="inlineStr">
-        <is>
-          <t>66.42% (EWR)</t>
-        </is>
-      </c>
-      <c r="I18" s="31" t="inlineStr">
-        <is>
-          <t>48.61%</t>
-        </is>
-      </c>
-      <c r="J18" s="31" t="inlineStr">
-        <is>
-          <t>+8.1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>BTS DB1B Surveys</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>True Local Originating TSA Demand</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>pax</t>
-        </is>
-      </c>
-      <c r="D19" s="26" t="n">
-        <v>16376561</v>
-      </c>
-      <c r="E19" s="26" t="n">
-        <v>5167458</v>
-      </c>
-      <c r="F19" s="26" t="n">
-        <v>15995278</v>
-      </c>
-      <c r="G19" s="9" t="inlineStr">
-        <is>
-          <t>10,555,299 (DTW)</t>
-        </is>
-      </c>
-      <c r="H19" s="9" t="inlineStr">
-        <is>
-          <t>26,293,897 (LAX)</t>
-        </is>
-      </c>
-      <c r="I19" s="26" t="n">
-        <v>13103484</v>
-      </c>
-      <c r="J19" s="31" t="inlineStr">
-        <is>
-          <t>+25.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>T-100 Aircraft Gauge</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>Seating Capacity per Flight</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>seats</t>
-        </is>
-      </c>
-      <c r="D20" s="29" t="n">
-        <v>168.42</v>
-      </c>
-      <c r="E20" s="29" t="n">
-        <v>7.49</v>
-      </c>
-      <c r="F20" s="29" t="n">
-        <v>168</v>
-      </c>
-      <c r="G20" s="9" t="inlineStr">
-        <is>
-          <t>154.20 (LGA)</t>
-        </is>
-      </c>
-      <c r="H20" s="9" t="inlineStr">
-        <is>
-          <t>182.30 (LAX)</t>
-        </is>
-      </c>
-      <c r="I20" s="29" t="n">
-        <v>171.1</v>
-      </c>
-      <c r="J20" s="31" t="inlineStr">
-        <is>
-          <t>-1.6%</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="13" t="inlineStr">
-        <is>
-          <t>T-100 Load Factor</t>
-        </is>
-      </c>
-      <c r="B21" s="13" t="inlineStr">
-        <is>
-          <t>Route Passenger Load Factor</t>
-        </is>
-      </c>
-      <c r="C21" s="13" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D21" s="32" t="inlineStr">
-        <is>
-          <t>85.08%</t>
-        </is>
-      </c>
-      <c r="E21" s="32" t="inlineStr">
-        <is>
-          <t>0.82%</t>
-        </is>
-      </c>
-      <c r="F21" s="32" t="inlineStr">
-        <is>
-          <t>85.26%</t>
-        </is>
-      </c>
-      <c r="G21" s="13" t="inlineStr">
-        <is>
-          <t>83.85% (DTW)</t>
-        </is>
-      </c>
-      <c r="H21" s="13" t="inlineStr">
-        <is>
-          <t>86.12% (EWR)</t>
-        </is>
-      </c>
-      <c r="I21" s="32" t="inlineStr">
-        <is>
-          <t>84.73%</t>
-        </is>
-      </c>
-      <c r="J21" s="32" t="inlineStr">
-        <is>
-          <t>+0.4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="28" t="inlineStr">
-        <is>
-          <t>Note. Formal Welch's two-sample t-tests demonstrating no statistically significant differences between the 9-airport experimental cohort and the Top 25 airport universe across operational metrics (all p &gt; 0.05).</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="rId1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2807,7 +1627,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3048,7 +1868,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3318,7 +2138,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3923,7 +2743,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4175,7 +2995,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4443,7 +3263,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4711,7 +3531,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4914,7 +3734,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6069,210 +4889,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="58" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="23" t="inlineStr">
-        <is>
-          <t>⬅ Return to Table of Contents</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="24" t="inlineStr">
-        <is>
-          <t>Table 4.3a</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="25" t="inlineStr">
-        <is>
-          <t>Post-Pandemic Temporal Demarcation Evaluation Across the Top 25 Network</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="10" customHeight="1"/>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Evaluation Criteria</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Candidate A: Mature Post-Pandemic</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Candidate B: Early Post-Mask Regime (Selected)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>Start Date</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>January 1, 2023</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>May 1, 2022 (RECOMMENDED)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>Statistical Demarcation Rationale</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>Rolling Welch's t-test variance convergence</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>CUSUM structural break stabilization; Mask Mandate Repeal</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>Training Span</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>24 Months (2023-01 to 2024-12)</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>32 Months (2022-05 to 2024-12; 20 mo train / 12 mo val)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>Holdout Test Span</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>12 Months (2025 Full-Year Holdout)</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>12 Months (2025 Full-Year Holdout)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>Robustness Impact</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>Excellent baseline stability; limited historical depth</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>Superior: Captures two complete annual seasonal cycles</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>Resilience Impact</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>Misses Winter Storm Elliott (Dec 2022)</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>Superior: Encapsulates severe winter freeze and summer storms</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>Generalizability Impact</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>Narrower training variance across spoke airfields</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>Superior: 404,324 candidate multi-facility hourly records</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>Coupling Rebound (R^2)</t>
-        </is>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>R^2 = 0.323 (Macro scheduled-to-TSA daily)</t>
-        </is>
-      </c>
-      <c r="C13" s="13" t="inlineStr">
-        <is>
-          <t>R^2 rebounds from 0.368 (COVID) to 0.306–0.323 (Equilibrium)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="28" t="inlineStr">
-        <is>
-          <t>Note. Empirical evaluation of post-pandemic temporal demarcation regimes. Candidate B (May 1, 2022 to December 31, 2025; 44 months, N = 1,341 days) was formally selected for maximum statistical power while preserving structural stability.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="rId1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -6299,14 +4915,14 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>Table 4.3b</t>
+          <t>Table 4.3</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="25" t="inlineStr">
         <is>
-          <t>Master Annual Seasonal Volatility Regimes Summary (Top 25 Airfields)</t>
+          <t>Master Annual Seasonal Volatility Regimes Summary Across the Top 25 Network</t>
         </is>
       </c>
     </row>
@@ -6579,7 +5195,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6610,14 +5226,14 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>Table 4.4a</t>
+          <t>Table 4.4</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="25" t="inlineStr">
         <is>
-          <t>Day-of-Week Volatility Dynamics and Operational Archetypes (Top 25 Airfields)</t>
+          <t>Master Day-of-Week Operational Volatility Regimes and Archetypes</t>
         </is>
       </c>
     </row>
@@ -6983,7 +5599,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7595,7 +6211,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8018,4 +6634,858 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="37" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="7" max="7"/>
+    <col width="27" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>⬅ Return to Table of Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="24" t="inlineStr">
+        <is>
+          <t>Table 4.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="25" t="inlineStr">
+        <is>
+          <t>Summary Descriptive Statistics: Nine-Airport Experimental Cohort Versus Top 25 Universe</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="10" customHeight="1"/>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Metric Category</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Operational Metric</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>9-Airport Mean</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>9-Airport Std Dev</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>9-Airport Median</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>9-Airport Min (Airport)</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>9-Airport Max (Airport)</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>Top 25 Mean</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>Delta (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>BTS OTP Operations</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Scheduled Domestic Flights</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>flights</t>
+        </is>
+      </c>
+      <c r="D6" s="26" t="n">
+        <v>224576</v>
+      </c>
+      <c r="E6" s="26" t="n">
+        <v>78441</v>
+      </c>
+      <c r="F6" s="26" t="n">
+        <v>206024</v>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>138,372 (PHL)</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>360,571 (ORD)</t>
+        </is>
+      </c>
+      <c r="I6" s="26" t="n">
+        <v>192160</v>
+      </c>
+      <c r="J6" s="31" t="inlineStr">
+        <is>
+          <t>+16.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>BTS OTP Operations</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Cancelled Flights</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>flights</t>
+        </is>
+      </c>
+      <c r="D7" s="26" t="n">
+        <v>3623</v>
+      </c>
+      <c r="E7" s="26" t="n">
+        <v>1599</v>
+      </c>
+      <c r="F7" s="26" t="n">
+        <v>2920</v>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>1,777 (DTW)</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>6,515 (DFW)</t>
+        </is>
+      </c>
+      <c r="I7" s="26" t="n">
+        <v>2738</v>
+      </c>
+      <c r="J7" s="31" t="inlineStr">
+        <is>
+          <t>+32.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>BTS OTP Operations</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>Flight Cancellation Rate</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D8" s="31" t="inlineStr">
+        <is>
+          <t>1.63%</t>
+        </is>
+      </c>
+      <c r="E8" s="31" t="inlineStr">
+        <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="F8" s="31" t="inlineStr">
+        <is>
+          <t>1.47%</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>0.99% (LAX)</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>2.46% (LGA)</t>
+        </is>
+      </c>
+      <c r="I8" s="31" t="inlineStr">
+        <is>
+          <t>1.43%</t>
+        </is>
+      </c>
+      <c r="J8" s="31" t="inlineStr">
+        <is>
+          <t>+14.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>BTS OTP Delays</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Average Departure Delay</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="D9" s="29" t="n">
+        <v>15.23</v>
+      </c>
+      <c r="E9" s="29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="F9" s="29" t="n">
+        <v>15.65</v>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>11.55 (DTW)</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>19.85 (DFW)</t>
+        </is>
+      </c>
+      <c r="I9" s="29" t="n">
+        <v>14.21</v>
+      </c>
+      <c r="J9" s="31" t="inlineStr">
+        <is>
+          <t>+7.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>BTS OTP Delays</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Significant Delay Rate (&gt;= 15m)</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D10" s="31" t="inlineStr">
+        <is>
+          <t>21.42%</t>
+        </is>
+      </c>
+      <c r="E10" s="31" t="inlineStr">
+        <is>
+          <t>3.30%</t>
+        </is>
+      </c>
+      <c r="F10" s="31" t="inlineStr">
+        <is>
+          <t>20.14%</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>17.93% (LAX)</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>28.07% (DFW)</t>
+        </is>
+      </c>
+      <c r="I10" s="31" t="inlineStr">
+        <is>
+          <t>20.31%</t>
+        </is>
+      </c>
+      <c r="J10" s="31" t="inlineStr">
+        <is>
+          <t>+5.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>BTS OTP Delays</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Runway Taxi-Out Queue Time</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="D11" s="29" t="n">
+        <v>20.59</v>
+      </c>
+      <c r="E11" s="29" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="F11" s="29" t="n">
+        <v>20.35</v>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>16.96 (DTW)</t>
+        </is>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>24.67 (EWR)</t>
+        </is>
+      </c>
+      <c r="I11" s="29" t="n">
+        <v>19.69</v>
+      </c>
+      <c r="J11" s="31" t="inlineStr">
+        <is>
+          <t>+4.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>TSA Checkpoint</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>Total Passenger Throughput</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>pax</t>
+        </is>
+      </c>
+      <c r="D12" s="26" t="n">
+        <v>71145628</v>
+      </c>
+      <c r="E12" s="26" t="n">
+        <v>27465238</v>
+      </c>
+      <c r="F12" s="26" t="n">
+        <v>63720916</v>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>40,429,531 (PHL)</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>129,069,341 (LAX)</t>
+        </is>
+      </c>
+      <c r="I12" s="26" t="n">
+        <v>68495531</v>
+      </c>
+      <c r="J12" s="31" t="inlineStr">
+        <is>
+          <t>+3.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>TSA Checkpoint</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Average Daily Passenger Count</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>pax/day</t>
+        </is>
+      </c>
+      <c r="D13" s="26" t="n">
+        <v>53075</v>
+      </c>
+      <c r="E13" s="26" t="n">
+        <v>20473</v>
+      </c>
+      <c r="F13" s="26" t="n">
+        <v>47553</v>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>30,171 (PHL)</t>
+        </is>
+      </c>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>96,249 (LAX)</t>
+        </is>
+      </c>
+      <c r="I13" s="26" t="n">
+        <v>51138</v>
+      </c>
+      <c r="J13" s="31" t="inlineStr">
+        <is>
+          <t>+3.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>TSA Checkpoint</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>Average Hourly Passenger Count</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>pax/hr</t>
+        </is>
+      </c>
+      <c r="D14" s="29" t="n">
+        <v>418.53</v>
+      </c>
+      <c r="E14" s="29" t="n">
+        <v>157.02</v>
+      </c>
+      <c r="F14" s="29" t="n">
+        <v>388.4</v>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>239.60 (ORD)</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>662.40 (LGA)</t>
+        </is>
+      </c>
+      <c r="I14" s="29" t="n">
+        <v>540.34</v>
+      </c>
+      <c r="J14" s="31" t="inlineStr">
+        <is>
+          <t>-22.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>TSA Checkpoint</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Peak Single-Hour Checkpoint Rush</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>pax/hr</t>
+        </is>
+      </c>
+      <c r="D15" s="26" t="n">
+        <v>2673</v>
+      </c>
+      <c r="E15" s="26" t="n">
+        <v>881</v>
+      </c>
+      <c r="F15" s="26" t="n">
+        <v>2654</v>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>1,385 (DTW)</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>4,020 (EWR)</t>
+        </is>
+      </c>
+      <c r="I15" s="26" t="n">
+        <v>2784</v>
+      </c>
+      <c r="J15" s="31" t="inlineStr">
+        <is>
+          <t>-4.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>TSA Checkpoint</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Demand Volatility (CV_TSA)</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="D16" s="36" t="n">
+        <v>0.8728</v>
+      </c>
+      <c r="E16" s="36" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F16" s="36" t="n">
+        <v>0.9064</v>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>0.6488 (BOS)</t>
+        </is>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>1.1240 (LGA)</t>
+        </is>
+      </c>
+      <c r="I16" s="36" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="J16" s="31" t="inlineStr">
+        <is>
+          <t>+5.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>BTS DB1B Surveys</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Connecting Passenger Share</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D17" s="31" t="inlineStr">
+        <is>
+          <t>47.45%</t>
+        </is>
+      </c>
+      <c r="E17" s="31" t="inlineStr">
+        <is>
+          <t>10.98%</t>
+        </is>
+      </c>
+      <c r="F17" s="31" t="inlineStr">
+        <is>
+          <t>44.41%</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>33.58% (EWR)</t>
+        </is>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>66.32% (DFW)</t>
+        </is>
+      </c>
+      <c r="I17" s="31" t="inlineStr">
+        <is>
+          <t>51.39%</t>
+        </is>
+      </c>
+      <c r="J17" s="31" t="inlineStr">
+        <is>
+          <t>-7.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>BTS DB1B Surveys</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>Local Originating Passenger Share</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D18" s="31" t="inlineStr">
+        <is>
+          <t>52.55%</t>
+        </is>
+      </c>
+      <c r="E18" s="31" t="inlineStr">
+        <is>
+          <t>10.98%</t>
+        </is>
+      </c>
+      <c r="F18" s="31" t="inlineStr">
+        <is>
+          <t>55.59%</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>33.68% (DFW)</t>
+        </is>
+      </c>
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>66.42% (EWR)</t>
+        </is>
+      </c>
+      <c r="I18" s="31" t="inlineStr">
+        <is>
+          <t>48.61%</t>
+        </is>
+      </c>
+      <c r="J18" s="31" t="inlineStr">
+        <is>
+          <t>+8.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>BTS DB1B Surveys</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>True Local Originating TSA Demand</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>pax</t>
+        </is>
+      </c>
+      <c r="D19" s="26" t="n">
+        <v>16376561</v>
+      </c>
+      <c r="E19" s="26" t="n">
+        <v>5167458</v>
+      </c>
+      <c r="F19" s="26" t="n">
+        <v>15995278</v>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>10,555,299 (DTW)</t>
+        </is>
+      </c>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>26,293,897 (LAX)</t>
+        </is>
+      </c>
+      <c r="I19" s="26" t="n">
+        <v>13103484</v>
+      </c>
+      <c r="J19" s="31" t="inlineStr">
+        <is>
+          <t>+25.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>T-100 Aircraft Gauge</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>Seating Capacity per Flight</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>seats</t>
+        </is>
+      </c>
+      <c r="D20" s="29" t="n">
+        <v>168.42</v>
+      </c>
+      <c r="E20" s="29" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="F20" s="29" t="n">
+        <v>168</v>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>154.20 (LGA)</t>
+        </is>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>182.30 (LAX)</t>
+        </is>
+      </c>
+      <c r="I20" s="29" t="n">
+        <v>171.1</v>
+      </c>
+      <c r="J20" s="31" t="inlineStr">
+        <is>
+          <t>-1.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>T-100 Load Factor</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>Route Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D21" s="32" t="inlineStr">
+        <is>
+          <t>85.08%</t>
+        </is>
+      </c>
+      <c r="E21" s="32" t="inlineStr">
+        <is>
+          <t>0.82%</t>
+        </is>
+      </c>
+      <c r="F21" s="32" t="inlineStr">
+        <is>
+          <t>85.26%</t>
+        </is>
+      </c>
+      <c r="G21" s="13" t="inlineStr">
+        <is>
+          <t>83.85% (DTW)</t>
+        </is>
+      </c>
+      <c r="H21" s="13" t="inlineStr">
+        <is>
+          <t>86.12% (EWR)</t>
+        </is>
+      </c>
+      <c r="I21" s="32" t="inlineStr">
+        <is>
+          <t>84.73%</t>
+        </is>
+      </c>
+      <c r="J21" s="32" t="inlineStr">
+        <is>
+          <t>+0.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="28" t="inlineStr">
+        <is>
+          <t>Note. Formal Welch's two-sample t-tests demonstrating no statistically significant differences between the 9-airport experimental cohort and the Top 25 airport universe across operational metrics (all p &gt; 0.05).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/tables and figures/results/thesis_tables.xlsx
+++ b/tables and figures/results/thesis_tables.xlsx
@@ -11,20 +11,21 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table-format" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_1" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_2" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_3" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_4" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_5" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_6" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_7" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_8" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_9" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_10" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_11" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_5_1" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_5_2" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_5_3" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_5_4" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dual_track_policy" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_3a" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_3b" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_4a" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_5" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_6" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_7" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_8" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_9" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_10" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_11" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_5_1" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_5_2" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_5_3" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_5_4" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dual_track_policy" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -38,7 +39,7 @@
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -96,31 +97,6 @@
       <name val="Calibri"/>
       <i val="1"/>
       <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <sz val="16"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <i val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="000000FF"/>
-      <sz val="11"/>
-      <u val="single"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -182,7 +158,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -289,16 +265,6 @@
     <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -664,428 +630,788 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:G25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="92" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="73" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="40" t="inlineStr">
-        <is>
-          <t>MASTER THESIS RESULTS &amp; FINDINGS TABLES</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="41" t="inlineStr">
-        <is>
-          <t>Evaluating Predictive Techniques to Model Stochastic Airport Passenger Flow | Gleich 700B</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="A4" s="42" t="inlineStr">
-        <is>
-          <t>Table Number</t>
-        </is>
-      </c>
-      <c r="B4" s="42" t="inlineStr">
-        <is>
-          <t>Sheet Name</t>
-        </is>
-      </c>
-      <c r="C4" s="42" t="inlineStr">
-        <is>
-          <t>Table Title</t>
-        </is>
-      </c>
-      <c r="D4" s="42" t="inlineStr">
-        <is>
-          <t>Chapter / Operational Scope</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="43" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>THESIS MASTER EMPIRICAL TABLES CATALOG (thesis_tables.xlsx)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Evaluating Predictive Techniques to Model Stochastic Airport Passenger Flow | MSAA / Gleich 700B | Leila Gleich</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Interactive Table Index: Click any Sheet Name or Table ID to navigate directly to that table. Every worksheet includes a '⬅ Return to Table of Contents' link in Cell A1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="10" customHeight="1"/>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Table ID</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Sheet Tab (Click to Jump)</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Official Manuscript Table Title</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Manuscript Chapter</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Dimensions</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Operational Scope &amp; Core Finding</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Evaluation Dimension</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Template</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>table-format</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>APA Style Reference Template (Demographic Characteristics)</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Results Appendix</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>8 rows x 4 cols</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>APA 7th Edition Sample Table Template (Clean boundary rules, no filters, no fill)</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>Formatting Specification</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>Table 4.1</t>
         </is>
       </c>
-      <c r="B5" s="44" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>table_4_1</t>
         </is>
       </c>
-      <c r="C5" s="45" t="inlineStr">
-        <is>
-          <t>Master Post-ETL Multi-Source Data Foundation Census</t>
-        </is>
-      </c>
-      <c r="D5" s="46" t="inlineStr">
-        <is>
-          <t>Chapter IV: Findings (Data Foundation)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="43" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Master Post-ETL Multi-Source Data Foundation Census (Full Candidate Commercial Network)</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Chapter 4: Results</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>5 rows x 6 cols</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>Census of 4 conformed federal feeds (TSA FOIA, BTS OTP, BTS T-100, BTS DB1B) covering 42,062,039 records</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>Data Foundation &amp; ETL Census</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>Table 4.2</t>
         </is>
       </c>
-      <c r="B6" s="44" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>table_4_2</t>
         </is>
       </c>
-      <c r="C6" s="45" t="inlineStr">
-        <is>
-          <t>Post-ETL Master Summary Descriptive Statistics</t>
-        </is>
-      </c>
-      <c r="D6" s="46" t="inlineStr">
-        <is>
-          <t>Chapter IV: Findings (Descriptive Scale)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="43" t="inlineStr">
-        <is>
-          <t>Table 4.3</t>
-        </is>
-      </c>
-      <c r="B7" s="44" t="inlineStr">
-        <is>
-          <t>table_4_3</t>
-        </is>
-      </c>
-      <c r="C7" s="45" t="inlineStr">
-        <is>
-          <t>Master Annual Seasonal Volatility Regimes Summary</t>
-        </is>
-      </c>
-      <c r="D7" s="46" t="inlineStr">
-        <is>
-          <t>Chapter IV: Findings (Annual Regimes)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="43" t="inlineStr">
-        <is>
-          <t>Table 4.4</t>
-        </is>
-      </c>
-      <c r="B8" s="44" t="inlineStr">
-        <is>
-          <t>table_4_4</t>
-        </is>
-      </c>
-      <c r="C8" s="45" t="inlineStr">
-        <is>
-          <t>Master Day-of-Week Operational Volatility Regimes</t>
-        </is>
-      </c>
-      <c r="D8" s="46" t="inlineStr">
-        <is>
-          <t>Chapter IV: Findings (DOW Archetypes)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="43" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Post-ETL Master Summary Descriptive Statistics (Top 25 Cleaned Data Warehouse)</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>Chapter 4: Results</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>11 rows x 11 cols</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>Master descriptive moments (mean, std dev, median, IQR, skewness, kurtosis) across all operational variables</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>Descriptive Statistics</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Table 4.3a</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>table_4_3a</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Post-Pandemic Temporal Demarcation Evaluation Across the Top 25 Network</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>Chapter 4: Results</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>8 rows x 3 cols</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>Comparison of Candidate A (Mature Post-Pandemic) and Candidate B (Early Post-Mask Regime; Selected, 44 months)</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>Temporal Demarcation</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Table 4.3b</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>table_4_3b</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Master Annual Seasonal Volatility Regimes Summary (Top 25 Airfields)</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>Chapter 4: Results</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>4 rows x 11 cols</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>Annual seasonal volatility regimes (Off-Peak, Mid-Peak, Peak, Holiday) across 1,341 post-demarcation days</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>Seasonality &amp; Volatility Regimes</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Table 4.4a</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>table_4_4a</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Day-of-Week Volatility Dynamics and Operational Archetypes (Top 25 Airfields)</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>Chapter 4: Results</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>7 rows x 10 cols</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>Weekly cyclical dynamics and operational archetypes across Monday through Sunday</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>Weekly Cyclical Dynamics</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>Table 4.5</t>
         </is>
       </c>
-      <c r="B9" s="44" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>table_4_5</t>
         </is>
       </c>
-      <c r="C9" s="45" t="inlineStr">
-        <is>
-          <t>Master Cross-Dataset Econometric Relationships</t>
-        </is>
-      </c>
-      <c r="D9" s="46" t="inlineStr">
-        <is>
-          <t>Chapter IV: Findings (Econometric Coupling)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="43" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Master Cross-Dataset Econometric Relationships (Top 25 Airfields)</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>Chapter 4: Results</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>12 rows x 9 cols</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>Econometric coupling between TSA checkpoint volumes and BTS OTP delays/capacity across 12 operational dimensions</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>Econometric Coupling</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Table 4.6</t>
         </is>
       </c>
-      <c r="B10" s="44" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>table_4_6</t>
         </is>
       </c>
-      <c r="C10" s="45" t="inlineStr">
-        <is>
-          <t>Nine-Airport Experimental Cohort Factorial Specification</t>
-        </is>
-      </c>
-      <c r="D10" s="46" t="inlineStr">
-        <is>
-          <t>Chapter IV: Findings (4x4 Matrix)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="43" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>The Nine-Airport Experimental Cohort Factorial Specification</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>Chapter 4: Results</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>9 rows x 7 cols</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>Balanced 4x4 factorial design across 12 carrier-exclusive complexes at 9 hubs (BOS, DFW, DTW, EWR, IAH, LAX, LGA, ORD, PHL)</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>Experimental Cohort Design</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>Table 4.7</t>
         </is>
       </c>
-      <c r="B11" s="44" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>table_4_7</t>
         </is>
       </c>
-      <c r="C11" s="45" t="inlineStr">
-        <is>
-          <t>Summary Descriptive Statistics: Nine-Airport Cohort vs. Top 25</t>
-        </is>
-      </c>
-      <c r="D11" s="46" t="inlineStr">
-        <is>
-          <t>Chapter IV: Findings (Cohort Contrast)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="43" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Summary Descriptive Statistics: Nine-Airport Experimental Cohort Versus Top 25 Universe</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>Chapter 4: Results</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>16 rows x 10 cols</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>Formal comparison proving sample representativeness of the 9-airport experimental cohort against the Top 25 universe</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>Sample Representativeness</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Table 4.8</t>
         </is>
       </c>
-      <c r="B12" s="44" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>table_4_8</t>
         </is>
       </c>
-      <c r="C12" s="45" t="inlineStr">
-        <is>
-          <t>Day-of-Week Mean Daily Passenger Throughput Across Nine Airports</t>
-        </is>
-      </c>
-      <c r="D12" s="46" t="inlineStr">
-        <is>
-          <t>Chapter IV: Findings (Local DOW Scale)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="43" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Day-of-Week Mean Daily Passenger Throughput Across the Nine Selected Airports</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>Chapter 4: Results</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>9 rows x 12 cols</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>Local airport DOW profiles, weekly peak/trough days, and Peak/Trough ratios (highlighting LGA corporate profile = 2.30)</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>Local Airport Demand Profiles</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>Table 4.9</t>
         </is>
       </c>
-      <c r="B13" s="44" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>table_4_9</t>
         </is>
       </c>
-      <c r="C13" s="45" t="inlineStr">
-        <is>
-          <t>Empirical Lead-Lag Transfer Dynamics</t>
-        </is>
-      </c>
-      <c r="D13" s="46" t="inlineStr">
-        <is>
-          <t>Chapter IV: Findings (Show-Up Convolution)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="43" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>Empirical Lead-Lag Transfer Dynamics (Scheduled Flights Versus Checkpoint Demand)</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>Chapter 4: Results</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>7 rows x 5 cols</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>Asymmetric correlation and explanatory power across Lag t-1, Same-Hour t, Lead t+1, t+2, t+3, and convolved kernels</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>Lead-Lag Show-Up Dynamics</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>Table 4.10</t>
         </is>
       </c>
-      <c r="B14" s="44" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>table_4_10</t>
         </is>
       </c>
-      <c r="C14" s="45" t="inlineStr">
-        <is>
-          <t>Master Model Benchmark Matrix (2025 Full-Year Holdout)</t>
-        </is>
-      </c>
-      <c r="D14" s="46" t="inlineStr">
-        <is>
-          <t>Chapter IV: Findings (Model Accuracy)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="43" t="inlineStr">
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Master Model Benchmark Matrix for TSA Throughput Volatility (2025 Full-Year Out-of-Time Holdout)</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>Chapter 4: Results</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>4 rows x 10 cols</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>Master benchmark matrix across candidate predictive models and baseline control on 72,053 holdout observations</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>Model Evaluation (Holdout)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>Table 4.11</t>
         </is>
       </c>
-      <c r="B15" s="44" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>table_4_11</t>
         </is>
       </c>
-      <c r="C15" s="45" t="inlineStr">
-        <is>
-          <t>Master Multi-Pillar Hypothesis Evaluation Matrix</t>
-        </is>
-      </c>
-      <c r="D15" s="46" t="inlineStr">
-        <is>
-          <t>Chapter IV: Findings (Hypothesis 1 Test)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="43" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Master Multi-Pillar Hypothesis Evaluation Matrix Across the Four Models (Throughput Volatility)</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>Chapter 4: Results</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>11 rows x 9 cols</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>Formal empirical hypothesis test matrix across Robustness, Resilience, and Generalizability with explicit targets</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>Hypothesis Testing (H1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>Table 5.1</t>
         </is>
       </c>
-      <c r="B16" s="44" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>table_5_1</t>
         </is>
       </c>
-      <c r="C16" s="45" t="inlineStr">
-        <is>
-          <t>Evaluation Dimension 1: Routine Operational Accuracy (Robustness)</t>
-        </is>
-      </c>
-      <c r="D16" s="46" t="inlineStr">
-        <is>
-          <t>Chapter V: Analysis (Dimension 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="43" t="inlineStr">
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Evaluation Dimension 1: Routine Operational Accuracy Across the Candidate Models</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>Chapter 5: Discussion</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>4 rows x 8 cols</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>Robustness evaluation under nominal flight conditions (RMSE, MASE, stated target MASE &lt; 0.70, Diebold-Mariano test)</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>Dimension 1: Robustness</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>Table 5.2</t>
         </is>
       </c>
-      <c r="B17" s="44" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>table_5_2</t>
         </is>
       </c>
-      <c r="C17" s="45" t="inlineStr">
-        <is>
-          <t>Evaluation Dimension 2: Resilience Under Disruption (IROPS Regimes)</t>
-        </is>
-      </c>
-      <c r="D17" s="46" t="inlineStr">
-        <is>
-          <t>Chapter V: Analysis (Dimension 2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="43" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>Evaluation Dimension 2: Resilience and Shock Performance Under Severe Operational Disruption</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>Chapter 5: Discussion</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>4 rows x 9 cols</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>Resilience evaluation under severe weather ground stops and delay programs (RMSE, MASE, R_MASE ≈ 1.00, TTR &lt; 4.0h)</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
+        <is>
+          <t>Dimension 2: Resilience</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>Table 5.3</t>
         </is>
       </c>
-      <c r="B18" s="44" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>table_5_3</t>
         </is>
       </c>
-      <c r="C18" s="45" t="inlineStr">
-        <is>
-          <t>Evaluation Dimension 3: Generalizability Across Facilities (Zero-Shot)</t>
-        </is>
-      </c>
-      <c r="D18" s="46" t="inlineStr">
-        <is>
-          <t>Chapter V: Analysis (Dimension 3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="43" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Evaluation Dimension 3: Generalizability and Cross-Airport Transfer Performance</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>Chapter 5: Discussion</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>4 rows x 9 cols</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>Zero-shot spatial transfer evaluation from EWR to LGA without retraining (RMSE, RTR = 1.00, Delta MASE &lt;= 10.0%)</t>
+        </is>
+      </c>
+      <c r="G21" s="10" t="inlineStr">
+        <is>
+          <t>Dimension 3: Generalizability</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>Table 5.4</t>
         </is>
       </c>
-      <c r="B19" s="44" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>table_5_4</t>
         </is>
       </c>
-      <c r="C19" s="45" t="inlineStr">
-        <is>
-          <t>Master Asymmetric Trade-Off Matrix (H1 Synthesis)</t>
-        </is>
-      </c>
-      <c r="D19" s="46" t="inlineStr">
-        <is>
-          <t>Chapter V: Analysis (Master Trade-Offs)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="43" t="inlineStr">
-        <is>
-          <t>Dual-Track Policy</t>
-        </is>
-      </c>
-      <c r="B20" s="44" t="inlineStr">
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Master Asymmetric Trade-Off Matrix Across the Candidate Models</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>Chapter 5: Discussion</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>3 rows x 7 cols</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>Synthesis of architectural trade-offs demonstrating asymmetric performance strengths across the candidate models</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>Architectural Synthesis</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>Policy 5.1</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>dual_track_policy</t>
         </is>
       </c>
-      <c r="C20" s="45" t="inlineStr">
-        <is>
-          <t>Dual-Track Operational Decision Playbook for Checkpoint Managers</t>
-        </is>
-      </c>
-      <c r="D20" s="46" t="inlineStr">
-        <is>
-          <t>Chapter V: Analysis (Operational Playbook)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="47" t="n"/>
-      <c r="B21" s="47" t="n"/>
-      <c r="C21" s="47" t="n"/>
-      <c r="D21" s="47" t="n"/>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>Dual-Track Operational Model Selection Policy</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>Chapter 5: Discussion</t>
+        </is>
+      </c>
+      <c r="E23" s="14" t="inlineStr">
+        <is>
+          <t>2 rows x 6 cols</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="inlineStr">
+        <is>
+          <t>Gated operational deployment rules for Gate 1 (Routine Flow Track -&gt; Model 2) and Gate 2 (Tactical Shock Track -&gt; Model 3)</t>
+        </is>
+      </c>
+      <c r="G23" s="14" t="inlineStr">
+        <is>
+          <t>Deployment Policy Matrix</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>Note. Master empirical table catalog conformed across Chapter IV (Results) and Chapter V (Discussion). Formatted according to APA Style (7th ed.) with horizontal boundary rules and no filter dropdowns.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId36"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1097,8 +1423,862 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="37" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="7" max="7"/>
+    <col width="27" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>⬅ Return to Table of Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="24" t="inlineStr">
+        <is>
+          <t>Table 4.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="25" t="inlineStr">
+        <is>
+          <t>Summary Descriptive Statistics: Nine-Airport Experimental Cohort Versus Top 25 Universe</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="10" customHeight="1"/>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Metric Category</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Operational Metric</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>9-Airport Mean</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>9-Airport Std Dev</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>9-Airport Median</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>9-Airport Min (Airport)</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>9-Airport Max (Airport)</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>Top 25 Mean</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>Delta (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>BTS OTP Operations</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Scheduled Domestic Flights</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>flights</t>
+        </is>
+      </c>
+      <c r="D6" s="26" t="n">
+        <v>224576</v>
+      </c>
+      <c r="E6" s="26" t="n">
+        <v>78441</v>
+      </c>
+      <c r="F6" s="26" t="n">
+        <v>206024</v>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>138,372 (PHL)</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>360,571 (ORD)</t>
+        </is>
+      </c>
+      <c r="I6" s="26" t="n">
+        <v>192160</v>
+      </c>
+      <c r="J6" s="31" t="inlineStr">
+        <is>
+          <t>+16.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>BTS OTP Operations</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Cancelled Flights</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>flights</t>
+        </is>
+      </c>
+      <c r="D7" s="26" t="n">
+        <v>3623</v>
+      </c>
+      <c r="E7" s="26" t="n">
+        <v>1599</v>
+      </c>
+      <c r="F7" s="26" t="n">
+        <v>2920</v>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>1,777 (DTW)</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>6,515 (DFW)</t>
+        </is>
+      </c>
+      <c r="I7" s="26" t="n">
+        <v>2738</v>
+      </c>
+      <c r="J7" s="31" t="inlineStr">
+        <is>
+          <t>+32.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>BTS OTP Operations</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>Flight Cancellation Rate</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D8" s="31" t="inlineStr">
+        <is>
+          <t>1.63%</t>
+        </is>
+      </c>
+      <c r="E8" s="31" t="inlineStr">
+        <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="F8" s="31" t="inlineStr">
+        <is>
+          <t>1.47%</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>0.99% (LAX)</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>2.46% (LGA)</t>
+        </is>
+      </c>
+      <c r="I8" s="31" t="inlineStr">
+        <is>
+          <t>1.43%</t>
+        </is>
+      </c>
+      <c r="J8" s="31" t="inlineStr">
+        <is>
+          <t>+14.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>BTS OTP Delays</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Average Departure Delay</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="D9" s="29" t="n">
+        <v>15.23</v>
+      </c>
+      <c r="E9" s="29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="F9" s="29" t="n">
+        <v>15.65</v>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>11.55 (DTW)</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>19.85 (DFW)</t>
+        </is>
+      </c>
+      <c r="I9" s="29" t="n">
+        <v>14.21</v>
+      </c>
+      <c r="J9" s="31" t="inlineStr">
+        <is>
+          <t>+7.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>BTS OTP Delays</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Significant Delay Rate (&gt;= 15m)</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D10" s="31" t="inlineStr">
+        <is>
+          <t>21.42%</t>
+        </is>
+      </c>
+      <c r="E10" s="31" t="inlineStr">
+        <is>
+          <t>3.30%</t>
+        </is>
+      </c>
+      <c r="F10" s="31" t="inlineStr">
+        <is>
+          <t>20.14%</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>17.93% (LAX)</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>28.07% (DFW)</t>
+        </is>
+      </c>
+      <c r="I10" s="31" t="inlineStr">
+        <is>
+          <t>20.31%</t>
+        </is>
+      </c>
+      <c r="J10" s="31" t="inlineStr">
+        <is>
+          <t>+5.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>BTS OTP Delays</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Runway Taxi-Out Queue Time</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="D11" s="29" t="n">
+        <v>20.59</v>
+      </c>
+      <c r="E11" s="29" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="F11" s="29" t="n">
+        <v>20.35</v>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>16.96 (DTW)</t>
+        </is>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>24.67 (EWR)</t>
+        </is>
+      </c>
+      <c r="I11" s="29" t="n">
+        <v>19.69</v>
+      </c>
+      <c r="J11" s="31" t="inlineStr">
+        <is>
+          <t>+4.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>TSA Checkpoint</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>Total Passenger Throughput</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>pax</t>
+        </is>
+      </c>
+      <c r="D12" s="26" t="n">
+        <v>71145628</v>
+      </c>
+      <c r="E12" s="26" t="n">
+        <v>27465238</v>
+      </c>
+      <c r="F12" s="26" t="n">
+        <v>63720916</v>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>40,429,531 (PHL)</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>129,069,341 (LAX)</t>
+        </is>
+      </c>
+      <c r="I12" s="26" t="n">
+        <v>68495531</v>
+      </c>
+      <c r="J12" s="31" t="inlineStr">
+        <is>
+          <t>+3.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>TSA Checkpoint</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Average Daily Passenger Count</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>pax/day</t>
+        </is>
+      </c>
+      <c r="D13" s="26" t="n">
+        <v>53075</v>
+      </c>
+      <c r="E13" s="26" t="n">
+        <v>20473</v>
+      </c>
+      <c r="F13" s="26" t="n">
+        <v>47553</v>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>30,171 (PHL)</t>
+        </is>
+      </c>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>96,249 (LAX)</t>
+        </is>
+      </c>
+      <c r="I13" s="26" t="n">
+        <v>51138</v>
+      </c>
+      <c r="J13" s="31" t="inlineStr">
+        <is>
+          <t>+3.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>TSA Checkpoint</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>Average Hourly Passenger Count</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>pax/hr</t>
+        </is>
+      </c>
+      <c r="D14" s="29" t="n">
+        <v>418.53</v>
+      </c>
+      <c r="E14" s="29" t="n">
+        <v>157.02</v>
+      </c>
+      <c r="F14" s="29" t="n">
+        <v>388.4</v>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>239.60 (ORD)</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>662.40 (LGA)</t>
+        </is>
+      </c>
+      <c r="I14" s="29" t="n">
+        <v>540.34</v>
+      </c>
+      <c r="J14" s="31" t="inlineStr">
+        <is>
+          <t>-22.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>TSA Checkpoint</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Peak Single-Hour Checkpoint Rush</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>pax/hr</t>
+        </is>
+      </c>
+      <c r="D15" s="26" t="n">
+        <v>2673</v>
+      </c>
+      <c r="E15" s="26" t="n">
+        <v>881</v>
+      </c>
+      <c r="F15" s="26" t="n">
+        <v>2654</v>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>1,385 (DTW)</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>4,020 (EWR)</t>
+        </is>
+      </c>
+      <c r="I15" s="26" t="n">
+        <v>2784</v>
+      </c>
+      <c r="J15" s="31" t="inlineStr">
+        <is>
+          <t>-4.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>TSA Checkpoint</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Demand Volatility (CV_TSA)</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="D16" s="36" t="n">
+        <v>0.8728</v>
+      </c>
+      <c r="E16" s="36" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F16" s="36" t="n">
+        <v>0.9064</v>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>0.6488 (BOS)</t>
+        </is>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>1.1240 (LGA)</t>
+        </is>
+      </c>
+      <c r="I16" s="36" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="J16" s="31" t="inlineStr">
+        <is>
+          <t>+5.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>BTS DB1B Surveys</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Connecting Passenger Share</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D17" s="31" t="inlineStr">
+        <is>
+          <t>47.45%</t>
+        </is>
+      </c>
+      <c r="E17" s="31" t="inlineStr">
+        <is>
+          <t>10.98%</t>
+        </is>
+      </c>
+      <c r="F17" s="31" t="inlineStr">
+        <is>
+          <t>44.41%</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>33.58% (EWR)</t>
+        </is>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>66.32% (DFW)</t>
+        </is>
+      </c>
+      <c r="I17" s="31" t="inlineStr">
+        <is>
+          <t>51.39%</t>
+        </is>
+      </c>
+      <c r="J17" s="31" t="inlineStr">
+        <is>
+          <t>-7.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>BTS DB1B Surveys</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>Local Originating Passenger Share</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D18" s="31" t="inlineStr">
+        <is>
+          <t>52.55%</t>
+        </is>
+      </c>
+      <c r="E18" s="31" t="inlineStr">
+        <is>
+          <t>10.98%</t>
+        </is>
+      </c>
+      <c r="F18" s="31" t="inlineStr">
+        <is>
+          <t>55.59%</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>33.68% (DFW)</t>
+        </is>
+      </c>
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>66.42% (EWR)</t>
+        </is>
+      </c>
+      <c r="I18" s="31" t="inlineStr">
+        <is>
+          <t>48.61%</t>
+        </is>
+      </c>
+      <c r="J18" s="31" t="inlineStr">
+        <is>
+          <t>+8.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>BTS DB1B Surveys</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>True Local Originating TSA Demand</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>pax</t>
+        </is>
+      </c>
+      <c r="D19" s="26" t="n">
+        <v>16376561</v>
+      </c>
+      <c r="E19" s="26" t="n">
+        <v>5167458</v>
+      </c>
+      <c r="F19" s="26" t="n">
+        <v>15995278</v>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>10,555,299 (DTW)</t>
+        </is>
+      </c>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>26,293,897 (LAX)</t>
+        </is>
+      </c>
+      <c r="I19" s="26" t="n">
+        <v>13103484</v>
+      </c>
+      <c r="J19" s="31" t="inlineStr">
+        <is>
+          <t>+25.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>T-100 Aircraft Gauge</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>Seating Capacity per Flight</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>seats</t>
+        </is>
+      </c>
+      <c r="D20" s="29" t="n">
+        <v>168.42</v>
+      </c>
+      <c r="E20" s="29" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="F20" s="29" t="n">
+        <v>168</v>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>154.20 (LGA)</t>
+        </is>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>182.30 (LAX)</t>
+        </is>
+      </c>
+      <c r="I20" s="29" t="n">
+        <v>171.1</v>
+      </c>
+      <c r="J20" s="31" t="inlineStr">
+        <is>
+          <t>-1.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>T-100 Load Factor</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>Route Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D21" s="32" t="inlineStr">
+        <is>
+          <t>85.08%</t>
+        </is>
+      </c>
+      <c r="E21" s="32" t="inlineStr">
+        <is>
+          <t>0.82%</t>
+        </is>
+      </c>
+      <c r="F21" s="32" t="inlineStr">
+        <is>
+          <t>85.26%</t>
+        </is>
+      </c>
+      <c r="G21" s="13" t="inlineStr">
+        <is>
+          <t>83.85% (DTW)</t>
+        </is>
+      </c>
+      <c r="H21" s="13" t="inlineStr">
+        <is>
+          <t>86.12% (EWR)</t>
+        </is>
+      </c>
+      <c r="I21" s="32" t="inlineStr">
+        <is>
+          <t>84.73%</t>
+        </is>
+      </c>
+      <c r="J21" s="32" t="inlineStr">
+        <is>
+          <t>+0.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="28" t="inlineStr">
+        <is>
+          <t>Note. Formal Welch's two-sample t-tests demonstrating no statistically significant differences between the 9-airport experimental cohort and the Top 25 airport universe across operational metrics (all p &gt; 0.05).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:L16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -1627,14 +2807,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
@@ -1868,14 +3048,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
@@ -2138,14 +3318,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
@@ -2743,14 +3923,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
@@ -2984,274 +4164,6 @@
       <c r="A11" s="28" t="inlineStr">
         <is>
           <t>Note. Dimension 1 (Robustness) nominal baseline: departure delays &lt; 15 min and cancellations = 0. Stated target: MASE_routine &lt; 0.700. Model 3 achieves lowest RMSE (222.1 pax/hr); Model 2 wins Routine Pareto Efficiency (MASE = 0.680-0.700, low compute latency).</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="rId1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="41" customWidth="1" min="7" max="7"/>
-    <col width="32" customWidth="1" min="8" max="8"/>
-    <col width="58" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="23" t="inlineStr">
-        <is>
-          <t>⬅ Return to Table of Contents</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="24" t="inlineStr">
-        <is>
-          <t>Table 5.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="25" t="inlineStr">
-        <is>
-          <t>Evaluation Dimension 2: Resilience and Shock Performance Under Severe Operational Disruption</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="10" customHeight="1"/>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Model Family</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Model Name</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Operational Approach</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>RMSE_shock (pax/hr)</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>MASE_shock</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Disruption Multiplier (R_MASE)</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>Stated Target (R ~ 1.00, Lowest MASE)</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>Time-to-Recovery (TTR_shock)</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>Operational Status &amp; Resilience Behavior</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>Baseline Control</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>Baseline Control</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>Daily Persistence Benchmark (y_t-24)</t>
-        </is>
-      </c>
-      <c r="D6" s="38" t="n">
-        <v>398.2</v>
-      </c>
-      <c r="E6" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>Static Reference</t>
-        </is>
-      </c>
-      <c r="H6" s="9" t="inlineStr">
-        <is>
-          <t>8.4 hours</t>
-        </is>
-      </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>Static persistence benchmark; slow natural dissipation</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>Deterministic Schedule</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>Model 1</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>Deterministic Flight Schedule Model</t>
-        </is>
-      </c>
-      <c r="D7" s="38" t="n">
-        <v>412.8</v>
-      </c>
-      <c r="E7" s="33" t="n">
-        <v>1.082</v>
-      </c>
-      <c r="F7" s="29" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>Fails Target</t>
-        </is>
-      </c>
-      <c r="H7" s="9" t="inlineStr">
-        <is>
-          <t>7.8 hours</t>
-        </is>
-      </c>
-      <c r="I7" s="9" t="inlineStr">
-        <is>
-          <t>Blind to airside delay cascades; high disruption error</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>Machine Learning</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>Model 2</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>Supervised Machine Learning Model</t>
-        </is>
-      </c>
-      <c r="D8" s="38" t="n">
-        <v>318.4</v>
-      </c>
-      <c r="E8" s="33" t="n">
-        <v>0.8120000000000001</v>
-      </c>
-      <c r="F8" s="29" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="G8" s="9" t="inlineStr">
-        <is>
-          <t>Fails Multiplier</t>
-        </is>
-      </c>
-      <c r="H8" s="9" t="inlineStr">
-        <is>
-          <t>5.4 hours</t>
-        </is>
-      </c>
-      <c r="I8" s="9" t="inlineStr">
-        <is>
-          <t>Fragile collapse from "Empty Checkpoint Fallacy"</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>Dynamic Hybrid</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>Model 3</t>
-        </is>
-      </c>
-      <c r="C9" s="13" t="inlineStr">
-        <is>
-          <t>Dynamic Two-Stage Hybrid Model</t>
-        </is>
-      </c>
-      <c r="D9" s="39" t="n">
-        <v>254.2</v>
-      </c>
-      <c r="E9" s="34" t="n">
-        <v>0.694</v>
-      </c>
-      <c r="F9" s="35" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="G9" s="13" t="inlineStr">
-        <is>
-          <t>TARGET MET (WINNER)</t>
-        </is>
-      </c>
-      <c r="H9" s="13" t="inlineStr">
-        <is>
-          <t>2.8 hours</t>
-        </is>
-      </c>
-      <c r="I9" s="13" t="inlineStr">
-        <is>
-          <t>Decisive Winner: Live error feedback prevents collapse</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="28" t="inlineStr">
-        <is>
-          <t>Note. Dimension 2 (Resilience) disruption regime: departure delays &gt;= 45 min or cancellations &gt;= 5. Stated target: R_MASE ≈ 1.00, TTR &lt; 4.0 hours. Model 3 is decisive winner (R_MASE = 1.05, MASE_shock = 0.694, TTR = 2.8 hrs). Pure ML (Model 2) collapses (R = 2.14).</t>
         </is>
       </c>
     </row>
@@ -3270,7 +4182,275 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="41" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="58" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>⬅ Return to Table of Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="24" t="inlineStr">
+        <is>
+          <t>Table 5.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="25" t="inlineStr">
+        <is>
+          <t>Evaluation Dimension 2: Resilience and Shock Performance Under Severe Operational Disruption</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="10" customHeight="1"/>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Model Family</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Model Name</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Operational Approach</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>RMSE_shock (pax/hr)</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>MASE_shock</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Disruption Multiplier (R_MASE)</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Stated Target (R ~ 1.00, Lowest MASE)</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Time-to-Recovery (TTR_shock)</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>Operational Status &amp; Resilience Behavior</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>Baseline Control</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Baseline Control</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Daily Persistence Benchmark (y_t-24)</t>
+        </is>
+      </c>
+      <c r="D6" s="38" t="n">
+        <v>398.2</v>
+      </c>
+      <c r="E6" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>Static Reference</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>8.4 hours</t>
+        </is>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>Static persistence benchmark; slow natural dissipation</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>Deterministic Schedule</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Model 1</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Deterministic Flight Schedule Model</t>
+        </is>
+      </c>
+      <c r="D7" s="38" t="n">
+        <v>412.8</v>
+      </c>
+      <c r="E7" s="33" t="n">
+        <v>1.082</v>
+      </c>
+      <c r="F7" s="29" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>Fails Target</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>7.8 hours</t>
+        </is>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>Blind to airside delay cascades; high disruption error</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>Machine Learning</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>Model 2</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Supervised Machine Learning Model</t>
+        </is>
+      </c>
+      <c r="D8" s="38" t="n">
+        <v>318.4</v>
+      </c>
+      <c r="E8" s="33" t="n">
+        <v>0.8120000000000001</v>
+      </c>
+      <c r="F8" s="29" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>Fails Multiplier</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>5.4 hours</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>Fragile collapse from "Empty Checkpoint Fallacy"</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Dynamic Hybrid</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>Model 3</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Dynamic Two-Stage Hybrid Model</t>
+        </is>
+      </c>
+      <c r="D9" s="39" t="n">
+        <v>254.2</v>
+      </c>
+      <c r="E9" s="34" t="n">
+        <v>0.694</v>
+      </c>
+      <c r="F9" s="35" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>TARGET MET (WINNER)</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="inlineStr">
+        <is>
+          <t>2.8 hours</t>
+        </is>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>Decisive Winner: Live error feedback prevents collapse</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="28" t="inlineStr">
+        <is>
+          <t>Note. Dimension 2 (Resilience) disruption regime: departure delays &gt;= 45 min or cancellations &gt;= 5. Stated target: R_MASE ≈ 1.00, TTR &lt; 4.0 hours. Model 3 is decisive winner (R_MASE = 1.05, MASE_shock = 0.694, TTR = 2.8 hrs). Pure ML (Model 2) collapses (R = 2.14).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
@@ -3531,14 +4711,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="48" customWidth="1" min="2" max="2"/>
@@ -3734,14 +4914,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="47" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
@@ -3891,7 +5071,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8.83203125" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -4055,7 +5235,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
@@ -4281,7 +5461,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="38" customWidth="1" min="2" max="2"/>
@@ -4889,8 +6069,212 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="37" customWidth="1" min="1" max="1"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>⬅ Return to Table of Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="24" t="inlineStr">
+        <is>
+          <t>Table 4.3a</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="25" t="inlineStr">
+        <is>
+          <t>Post-Pandemic Temporal Demarcation Evaluation Across the Top 25 Network</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="10" customHeight="1"/>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Evaluation Criteria</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Candidate A: Mature Post-Pandemic</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Candidate B: Early Post-Mask Regime (Selected)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>Start Date</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>January 1, 2023</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>May 1, 2022 (RECOMMENDED)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>Statistical Demarcation Rationale</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Rolling Welch's t-test variance convergence</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>CUSUM structural break stabilization; Mask Mandate Repeal</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>Training Span</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>24 Months (2023-01 to 2024-12)</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>32 Months (2022-05 to 2024-12; 20 mo train / 12 mo val)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Holdout Test Span</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>12 Months (2025 Full-Year Holdout)</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>12 Months (2025 Full-Year Holdout)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>Robustness Impact</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Excellent baseline stability; limited historical depth</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Superior: Captures two complete annual seasonal cycles</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Resilience Impact</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Misses Winter Storm Elliott (Dec 2022)</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Superior: Encapsulates severe winter freeze and summer storms</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>Generalizability Impact</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>Narrower training variance across spoke airfields</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Superior: 404,324 candidate multi-facility hourly records</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>Coupling Rebound (R^2)</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>R^2 = 0.323 (Macro scheduled-to-TSA daily)</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>R^2 rebounds from 0.368 (COVID) to 0.306–0.323 (Equilibrium)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="28" t="inlineStr">
+        <is>
+          <t>Note. Empirical evaluation of post-pandemic temporal demarcation regimes. Candidate B (May 1, 2022 to December 31, 2025; 44 months, N = 1,341 days) was formally selected for maximum statistical power while preserving structural stability.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:K11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="44" customWidth="1" min="2" max="2"/>
@@ -4915,14 +6299,14 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>Table 4.3</t>
+          <t>Table 4.3b</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="25" t="inlineStr">
         <is>
-          <t>Master Annual Seasonal Volatility Regimes Summary Across the Top 25 Network</t>
+          <t>Master Annual Seasonal Volatility Regimes Summary (Top 25 Airfields)</t>
         </is>
       </c>
     </row>
@@ -5195,14 +6579,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -5226,14 +6610,14 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>Table 4.4</t>
+          <t>Table 4.4a</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="25" t="inlineStr">
         <is>
-          <t>Master Day-of-Week Operational Volatility Regimes and Archetypes</t>
+          <t>Day-of-Week Volatility Dynamics and Operational Archetypes (Top 25 Airfields)</t>
         </is>
       </c>
     </row>
@@ -5588,618 +6972,6 @@
       <c r="A14" s="28" t="inlineStr">
         <is>
           <t>Note. Day-of-week volatility dynamics aggregated across 1,341 calendar days and Top 25 airfields. N = 191 to 192 observations per day of week. CV represents the scale-free coefficient of variation.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="rId1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="60" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="23" t="inlineStr">
-        <is>
-          <t>⬅ Return to Table of Contents</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="24" t="inlineStr">
-        <is>
-          <t>Table 4.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="25" t="inlineStr">
-        <is>
-          <t>Master Cross-Dataset Econometric Relationships (Top 25 Airfields)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="10" customHeight="1"/>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Relationship Category</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Metric 1 (OTP / Capacity)</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Metric 2 (TSA Demand / Queue)</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Sample Grain</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Pearson r</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>R^2 (%)</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>t-statistic</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>p-value</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>Operational Significance &amp; Interpretation</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>Volume Coupling</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>Raw Scheduled Flight Departures</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>Total TSA Checkpoint Throughput</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>Top 25 Airfields</t>
-        </is>
-      </c>
-      <c r="E6" s="36" t="n">
-        <v>0.4572</v>
-      </c>
-      <c r="F6" s="31" t="inlineStr">
-        <is>
-          <t>20.90%</t>
-        </is>
-      </c>
-      <c r="G6" s="29" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="H6" s="9" t="inlineStr">
-        <is>
-          <t>&lt; 0.05</t>
-        </is>
-      </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>Modest linear coupling; scheduled flights alone explain only 20.9% of checkpoint passenger variance due to connecting passenger volume.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>Connecting Deflation</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>Raw Scheduled Flight Departures</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>True Local Originating TSA Demand</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="inlineStr">
-        <is>
-          <t>Top 25 Airfields</t>
-        </is>
-      </c>
-      <c r="E7" s="36" t="n">
-        <v>0.6704</v>
-      </c>
-      <c r="F7" s="31" t="inlineStr">
-        <is>
-          <t>44.94%</t>
-        </is>
-      </c>
-      <c r="G7" s="29" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="H7" s="9" t="inlineStr">
-        <is>
-          <t>&lt; 0.001</t>
-        </is>
-      </c>
-      <c r="I7" s="9" t="inlineStr">
-        <is>
-          <t>Strong linear coupling; removing connecting transfers via DB1B ticket surveys increases explained variance by +115% (from 20.9% to 44.9%).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>Hub Scale vs. Connecting</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>Connecting Passenger Ratio (%)</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>Scheduled Flight Volume</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>Top 25 Airfields</t>
-        </is>
-      </c>
-      <c r="E8" s="36" t="n">
-        <v>0.4503</v>
-      </c>
-      <c r="F8" s="31" t="inlineStr">
-        <is>
-          <t>20.28%</t>
-        </is>
-      </c>
-      <c r="G8" s="29" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="H8" s="9" t="inlineStr">
-        <is>
-          <t>&lt; 0.05</t>
-        </is>
-      </c>
-      <c r="I8" s="9" t="inlineStr">
-        <is>
-          <t>Hub scale effect; larger airline hub operations inherently possess higher connecting passenger fractions (e.g., CLT 76.0%, ATL 70.1%).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>Surface Queue Feedback</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>Runway Taxi-Out Queue Time (min)</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>Total TSA Checkpoint Throughput</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>Top 25 Airfields</t>
-        </is>
-      </c>
-      <c r="E9" s="36" t="n">
-        <v>0.2867</v>
-      </c>
-      <c r="F9" s="31" t="inlineStr">
-        <is>
-          <t>8.22%</t>
-        </is>
-      </c>
-      <c r="G9" s="29" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="H9" s="33" t="n">
-        <v>0.163</v>
-      </c>
-      <c r="I9" s="9" t="inlineStr">
-        <is>
-          <t>Directional trend; airports processing higher passenger volumes with larger aircraft experience longer tarmac taxi queues.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>Surface-to-Air Feedback</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>Mean Flight Departure Delay (min)</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>Runway Taxi-Out Queue Time (min)</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>63,925 Airport-Days</t>
-        </is>
-      </c>
-      <c r="E10" s="36" t="n">
-        <v>0.4971</v>
-      </c>
-      <c r="F10" s="31" t="inlineStr">
-        <is>
-          <t>24.71%</t>
-        </is>
-      </c>
-      <c r="G10" s="29" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="H10" s="9" t="inlineStr">
-        <is>
-          <t>&lt; 0.001</t>
-        </is>
-      </c>
-      <c r="I10" s="9" t="inlineStr">
-        <is>
-          <t>Delayed gate pushbacks compress outbound aircraft into congested runway sequencing queues.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>Schedule Delay Coupling</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>Significant Delays (DepDel15 %)</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>Total TSA Checkpoint Throughput</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>Top 25 Airfields</t>
-        </is>
-      </c>
-      <c r="E11" s="36" t="n">
-        <v>0.2019</v>
-      </c>
-      <c r="F11" s="31" t="inlineStr">
-        <is>
-          <t>4.08%</t>
-        </is>
-      </c>
-      <c r="G11" s="29" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="H11" s="33" t="n">
-        <v>0.332</v>
-      </c>
-      <c r="I11" s="9" t="inlineStr">
-        <is>
-          <t>Weak coupling; flight delay rates are primarily governed by convective weather and ATC ground delay programs rather than landside volume.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>Hourly Volatility Transmission</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>Hourly TSA Throughput Volatility (CV)</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>Flight Departure Delay Volatility (CV)</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>Top 25 Airfields</t>
-        </is>
-      </c>
-      <c r="E12" s="36" t="n">
-        <v>0.4375</v>
-      </c>
-      <c r="F12" s="31" t="inlineStr">
-        <is>
-          <t>19.14%</t>
-        </is>
-      </c>
-      <c r="G12" s="29" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="H12" s="9" t="inlineStr">
-        <is>
-          <t>&lt; 0.05</t>
-        </is>
-      </c>
-      <c r="I12" s="9" t="inlineStr">
-        <is>
-          <t>Direct operational coupling; spiky passenger arrivals at checkpoints inject variance into boarding gate closures and pushback times.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>Daily Volatility Coupling</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>Daily TSA Throughput Volatility (CV)</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>Flight Departure Delay Volatility (CV)</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>Top 25 Airfields</t>
-        </is>
-      </c>
-      <c r="E13" s="36" t="n">
-        <v>0.3714</v>
-      </c>
-      <c r="F13" s="31" t="inlineStr">
-        <is>
-          <t>13.79%</t>
-        </is>
-      </c>
-      <c r="G13" s="29" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="H13" s="33" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="I13" s="9" t="inlineStr">
-        <is>
-          <t>Day-to-day checkpoint throughput dispersion tracks daily flight departure delay dispersion across the network.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>Surge vs. Delay Volatility</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>Hourly TSA Peak-to-Median Surge Ratio</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>Flight Departure Delay Volatility (CV)</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>Top 25 Airfields</t>
-        </is>
-      </c>
-      <c r="E14" s="36" t="n">
-        <v>0.348</v>
-      </c>
-      <c r="F14" s="31" t="inlineStr">
-        <is>
-          <t>12.11%</t>
-        </is>
-      </c>
-      <c r="G14" s="29" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="H14" s="33" t="n">
-        <v>0.08799999999999999</v>
-      </c>
-      <c r="I14" s="9" t="inlineStr">
-        <is>
-          <t>Airfields with sharp peak-to-median checkpoint rushes experience heightened schedule volatility.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>Weekly Cyclical Coupling</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>Day-of-Week Mean Daily TSA Pax</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>Day-of-Week Mean Departure Delay (min)</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>7 Days (N=7)</t>
-        </is>
-      </c>
-      <c r="E15" s="36" t="n">
-        <v>0.9022</v>
-      </c>
-      <c r="F15" s="31" t="inlineStr">
-        <is>
-          <t>81.40%</t>
-        </is>
-      </c>
-      <c r="G15" s="29" t="n">
-        <v>4.68</v>
-      </c>
-      <c r="H15" s="9" t="inlineStr">
-        <is>
-          <t>&lt; 0.01</t>
-        </is>
-      </c>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>Deterministic weekly cadence; weekly passenger surge days (Sunday/Monday) explain 81.4% of weekly departure delay variance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>Weekly Delay Rate Coupling</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>Day-of-Week Mean Daily TSA Pax</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>Day-of-Week DepDel15 Rate (%)</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>7 Days (N=7)</t>
-        </is>
-      </c>
-      <c r="E16" s="36" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F16" s="31" t="inlineStr">
-        <is>
-          <t>81.00%</t>
-        </is>
-      </c>
-      <c r="G16" s="29" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="H16" s="9" t="inlineStr">
-        <is>
-          <t>&lt; 0.01</t>
-        </is>
-      </c>
-      <c r="I16" s="9" t="inlineStr">
-        <is>
-          <t>Weekly passenger volume peaks directly produce the week's highest flight delay rates (Sunday DepDel15 = 20.55%).</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="13" t="inlineStr">
-        <is>
-          <t>Annual Monthly Coupling</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="inlineStr">
-        <is>
-          <t>Monthly Mean Daily TSA Pax</t>
-        </is>
-      </c>
-      <c r="C17" s="13" t="inlineStr">
-        <is>
-          <t>Monthly Mean Departure Delay (min)</t>
-        </is>
-      </c>
-      <c r="D17" s="13" t="inlineStr">
-        <is>
-          <t>12 Months (N=12)</t>
-        </is>
-      </c>
-      <c r="E17" s="37" t="n">
-        <v>0.6313</v>
-      </c>
-      <c r="F17" s="32" t="inlineStr">
-        <is>
-          <t>39.85%</t>
-        </is>
-      </c>
-      <c r="G17" s="35" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="H17" s="13" t="inlineStr">
-        <is>
-          <t>&lt; 0.05</t>
-        </is>
-      </c>
-      <c r="I17" s="13" t="inlineStr">
-        <is>
-          <t>Summer peak alignment; summer passenger surges coincide with peak convective thunderstorm delays in June and July.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="28" t="inlineStr">
-        <is>
-          <t>Note. Econometric coupling between flight operational features and checkpoint throughput volatility. Checkpoint arrival volatility is coupled with departure delay volatility (r = +0.4373, p &lt; 0.05), while static delay minutes show no correlation (r = -0.062, p = 0.77).</t>
         </is>
       </c>
     </row>
@@ -6217,16 +6989,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:I19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="43" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="41" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -6239,14 +7013,14 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>Table 4.6</t>
+          <t>Table 4.5</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="25" t="inlineStr">
         <is>
-          <t>The Nine-Airport Experimental Cohort Factorial Specification</t>
+          <t>Master Cross-Dataset Econometric Relationships (Top 25 Airfields)</t>
         </is>
       </c>
     </row>
@@ -6254,377 +7028,562 @@
     <row r="5" ht="28" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Airport Code</t>
+          <t>Relationship Category</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Airport Name</t>
+          <t>Metric 1 (OTP / Capacity)</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Dominant Legacy Carrier</t>
+          <t>Metric 2 (TSA Demand / Queue)</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Carrier Hub Role</t>
+          <t>Sample Grain</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Dedicated Terminal Screening Complex</t>
+          <t>Pearson r</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Cluster Archetype</t>
+          <t>R^2 (%)</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>Strategic Justification &amp; Selection Rationale</t>
+          <t>t-statistic</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>p-value</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>Operational Significance &amp; Interpretation</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>BOS</t>
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>Volume Coupling</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Boston Logan</t>
+          <t>Raw Scheduled Flight Departures</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>DL / AA</t>
+          <t>Total TSA Checkpoint Throughput</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>Dual Focus Station</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>Terminal A (DL) &amp; Terminal B (AA)</t>
-        </is>
-      </c>
-      <c r="F6" s="9" t="inlineStr">
-        <is>
-          <t>Cluster 1: High-Density O&amp;D Focus</t>
-        </is>
-      </c>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>Unconfounded Northeast high-yield O&amp;D demand; physically separate terminal finger piers.</t>
+          <t>Top 25 Airfields</t>
+        </is>
+      </c>
+      <c r="E6" s="36" t="n">
+        <v>0.4572</v>
+      </c>
+      <c r="F6" s="31" t="inlineStr">
+        <is>
+          <t>20.90%</t>
+        </is>
+      </c>
+      <c r="G6" s="29" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>&lt; 0.05</t>
+        </is>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>Modest linear coupling; scheduled flights alone explain only 20.9% of checkpoint passenger variance due to connecting passenger volume.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>DFW</t>
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>Connecting Deflation</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Dallas/Fort Worth</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>AA</t>
+          <t>Raw Scheduled Flight Departures</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>True Local Originating TSA Demand</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>Primary Fortress Hub</t>
-        </is>
-      </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>Terminal D Screening Complex</t>
-        </is>
-      </c>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t>Cluster 0: Mega-Connecting Gateway</t>
-        </is>
-      </c>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>American Airlines primary mega-connecting fortress hub; high gauge international operations.</t>
+          <t>Top 25 Airfields</t>
+        </is>
+      </c>
+      <c r="E7" s="36" t="n">
+        <v>0.6704</v>
+      </c>
+      <c r="F7" s="31" t="inlineStr">
+        <is>
+          <t>44.94%</t>
+        </is>
+      </c>
+      <c r="G7" s="29" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>&lt; 0.001</t>
+        </is>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>Strong linear coupling; removing connecting transfers via DB1B ticket surveys increases explained variance by +115% (from 20.9% to 44.9%).</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>DTW</t>
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>Hub Scale vs. Connecting</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Detroit Metro</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>DL</t>
+          <t>Connecting Passenger Ratio (%)</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Scheduled Flight Volume</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>Primary Fortress Hub</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t>McNamara Terminal Complex</t>
-        </is>
-      </c>
-      <c r="F8" s="9" t="inlineStr">
-        <is>
-          <t>Cluster 2: High-Reliability Fortress</t>
-        </is>
-      </c>
-      <c r="G8" s="9" t="inlineStr">
-        <is>
-          <t>Delta primary Midwest fortress hub; world-class operational fluidity and high connecting ratio.</t>
+          <t>Top 25 Airfields</t>
+        </is>
+      </c>
+      <c r="E8" s="36" t="n">
+        <v>0.4503</v>
+      </c>
+      <c r="F8" s="31" t="inlineStr">
+        <is>
+          <t>20.28%</t>
+        </is>
+      </c>
+      <c r="G8" s="29" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>&lt; 0.05</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>Hub scale effect; larger airline hub operations inherently possess higher connecting passenger fractions (e.g., CLT 76.0%, ATL 70.1%).</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>EWR</t>
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Surface Queue Feedback</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Newark Liberty</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>UA</t>
+          <t>Runway Taxi-Out Queue Time (min)</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Total TSA Checkpoint Throughput</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>Primary Fortress Hub</t>
-        </is>
-      </c>
-      <c r="E9" s="9" t="inlineStr">
-        <is>
-          <t>Terminal C Screening Complex</t>
-        </is>
-      </c>
-      <c r="F9" s="9" t="inlineStr">
-        <is>
-          <t>Cluster 3: Congested Coastal Originator</t>
-        </is>
-      </c>
-      <c r="G9" s="9" t="inlineStr">
-        <is>
-          <t>United primary East Coast fortress hub; severe New York airspace slot congestion.</t>
+          <t>Top 25 Airfields</t>
+        </is>
+      </c>
+      <c r="E9" s="36" t="n">
+        <v>0.2867</v>
+      </c>
+      <c r="F9" s="31" t="inlineStr">
+        <is>
+          <t>8.22%</t>
+        </is>
+      </c>
+      <c r="G9" s="29" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="H9" s="33" t="n">
+        <v>0.163</v>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>Directional trend; airports processing higher passenger volumes with larger aircraft experience longer tarmac taxi queues.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>IAH</t>
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>Surface-to-Air Feedback</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Houston Bush</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>UA</t>
+          <t>Mean Flight Departure Delay (min)</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Runway Taxi-Out Queue Time (min)</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>Primary Fortress Hub</t>
-        </is>
-      </c>
-      <c r="E10" s="9" t="inlineStr">
-        <is>
-          <t>Terminal C Screening Complex</t>
-        </is>
-      </c>
-      <c r="F10" s="9" t="inlineStr">
-        <is>
-          <t>Cluster 1: High-Density O&amp;D Focus</t>
-        </is>
-      </c>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>United southern hub; balanced energy sector business O&amp;D travel and Latin American connecting banks.</t>
+          <t>Top 25 Airfields</t>
+        </is>
+      </c>
+      <c r="E10" s="36" t="n">
+        <v>0.4971</v>
+      </c>
+      <c r="F10" s="31" t="inlineStr">
+        <is>
+          <t>24.71%</t>
+        </is>
+      </c>
+      <c r="G10" s="29" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>&lt; 0.001</t>
+        </is>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>Delayed gate pushbacks compress outbound aircraft into congested runway sequencing queues.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>LAX</t>
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Delay Coupling</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Los Angeles World</t>
+          <t>Significant Delays (DepDel15 %)</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>DL / AA / UA</t>
+          <t>Total TSA Checkpoint Throughput</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>Tri-Carrier Parity Hub</t>
-        </is>
-      </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>Terminals 2/3 (DL), 4 (AA), 7 (UA)</t>
-        </is>
-      </c>
-      <c r="F11" s="9" t="inlineStr">
-        <is>
-          <t>Cluster 0: Mega-Connecting Gateway</t>
-        </is>
-      </c>
-      <c r="G11" s="9" t="inlineStr">
-        <is>
-          <t>Massive transpacific and transcontinental origin-destination demand across all three legacy carriers.</t>
+          <t>Top 25 Airfields</t>
+        </is>
+      </c>
+      <c r="E11" s="36" t="n">
+        <v>0.2019</v>
+      </c>
+      <c r="F11" s="31" t="inlineStr">
+        <is>
+          <t>4.08%</t>
+        </is>
+      </c>
+      <c r="G11" s="29" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="H11" s="33" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>Weak coupling; flight delay rates are primarily governed by convective weather and ATC ground delay programs rather than landside volume.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>LGA</t>
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>Hourly Volatility Transmission</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>New York LaGuardia</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>DL</t>
+          <t>Hourly TSA Throughput Volatility (CV)</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Flight Departure Delay Volatility (CV)</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>Primary Fortress Hub</t>
-        </is>
-      </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>Terminal C Screening Complex</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="inlineStr">
-        <is>
-          <t>Cluster 3: Congested Coastal Originator</t>
-        </is>
-      </c>
-      <c r="G12" s="9" t="inlineStr">
-        <is>
-          <t>Consolidated Delta Terminal C (opened June 2022); perimeter rule market and pure O&amp;D flows.</t>
+          <t>Top 25 Airfields</t>
+        </is>
+      </c>
+      <c r="E12" s="36" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="F12" s="31" t="inlineStr">
+        <is>
+          <t>19.14%</t>
+        </is>
+      </c>
+      <c r="G12" s="29" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>&lt; 0.05</t>
+        </is>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>Direct operational coupling; spiky passenger arrivals at checkpoints inject variance into boarding gate closures and pushback times.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>ORD</t>
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>Daily Volatility Coupling</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Chicago O'Hare</t>
+          <t>Daily TSA Throughput Volatility (CV)</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>UA / AA</t>
+          <t>Flight Departure Delay Volatility (CV)</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>Dual Fortress Hub</t>
-        </is>
-      </c>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>Terminal 1 (UA) &amp; Terminal 3 (AA)</t>
-        </is>
-      </c>
-      <c r="F13" s="9" t="inlineStr">
-        <is>
-          <t>Cluster 0: Mega-Connecting Gateway</t>
-        </is>
-      </c>
-      <c r="G13" s="9" t="inlineStr">
-        <is>
-          <t>Intense head-to-head legacy carrier competition; dual hub bank synchronization.</t>
+          <t>Top 25 Airfields</t>
+        </is>
+      </c>
+      <c r="E13" s="36" t="n">
+        <v>0.3714</v>
+      </c>
+      <c r="F13" s="31" t="inlineStr">
+        <is>
+          <t>13.79%</t>
+        </is>
+      </c>
+      <c r="G13" s="29" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="H13" s="33" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>Day-to-day checkpoint throughput dispersion tracks daily flight departure delay dispersion across the network.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="14" t="inlineStr">
-        <is>
-          <t>PHL</t>
-        </is>
-      </c>
-      <c r="B14" s="13" t="inlineStr">
-        <is>
-          <t>Philadelphia Intl</t>
-        </is>
-      </c>
-      <c r="C14" s="14" t="inlineStr">
-        <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="D14" s="13" t="inlineStr">
-        <is>
-          <t>Primary Fortress Hub</t>
-        </is>
-      </c>
-      <c r="E14" s="13" t="inlineStr">
-        <is>
-          <t>Terminals B &amp; C Complexes</t>
-        </is>
-      </c>
-      <c r="F14" s="13" t="inlineStr">
-        <is>
-          <t>Cluster 2: High-Reliability Fortress</t>
-        </is>
-      </c>
-      <c r="G14" s="13" t="inlineStr">
-        <is>
-          <t>American Mid-Atlantic transatlantic hub; counterpart to Delta's Midwestern fortress at DTW.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="28" t="inlineStr">
-        <is>
-          <t>Note. Balanced 4x4 factorial specification establishing the 9-airport experimental cohort across 12 carrier-exclusive complexes, controlling for physical checkpoint topology and hub banking structure.</t>
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>Surge vs. Delay Volatility</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>Hourly TSA Peak-to-Median Surge Ratio</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Flight Departure Delay Volatility (CV)</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>Top 25 Airfields</t>
+        </is>
+      </c>
+      <c r="E14" s="36" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="F14" s="31" t="inlineStr">
+        <is>
+          <t>12.11%</t>
+        </is>
+      </c>
+      <c r="G14" s="29" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="H14" s="33" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>Airfields with sharp peak-to-median checkpoint rushes experience heightened schedule volatility.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>Weekly Cyclical Coupling</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Day-of-Week Mean Daily TSA Pax</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Day-of-Week Mean Departure Delay (min)</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>7 Days (N=7)</t>
+        </is>
+      </c>
+      <c r="E15" s="36" t="n">
+        <v>0.9022</v>
+      </c>
+      <c r="F15" s="31" t="inlineStr">
+        <is>
+          <t>81.40%</t>
+        </is>
+      </c>
+      <c r="G15" s="29" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>&lt; 0.01</t>
+        </is>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>Deterministic weekly cadence; weekly passenger surge days (Sunday/Monday) explain 81.4% of weekly departure delay variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>Weekly Delay Rate Coupling</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Day-of-Week Mean Daily TSA Pax</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>Day-of-Week DepDel15 Rate (%)</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>7 Days (N=7)</t>
+        </is>
+      </c>
+      <c r="E16" s="36" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F16" s="31" t="inlineStr">
+        <is>
+          <t>81.00%</t>
+        </is>
+      </c>
+      <c r="G16" s="29" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>&lt; 0.01</t>
+        </is>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>Weekly passenger volume peaks directly produce the week's highest flight delay rates (Sunday DepDel15 = 20.55%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>Annual Monthly Coupling</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>Monthly Mean Daily TSA Pax</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>Monthly Mean Departure Delay (min)</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>12 Months (N=12)</t>
+        </is>
+      </c>
+      <c r="E17" s="37" t="n">
+        <v>0.6313</v>
+      </c>
+      <c r="F17" s="32" t="inlineStr">
+        <is>
+          <t>39.85%</t>
+        </is>
+      </c>
+      <c r="G17" s="35" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="H17" s="13" t="inlineStr">
+        <is>
+          <t>&lt; 0.05</t>
+        </is>
+      </c>
+      <c r="I17" s="13" t="inlineStr">
+        <is>
+          <t>Summer peak alignment; summer passenger surges coincide with peak convective thunderstorm delays in June and July.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="28" t="inlineStr">
+        <is>
+          <t>Note. Econometric coupling between flight operational features and checkpoint throughput volatility. Checkpoint arrival volatility is coupled with departure delay volatility (r = +0.4373, p &lt; 0.05), while static delay minutes show no correlation (r = -0.062, p = 0.77).</t>
         </is>
       </c>
     </row>
@@ -6642,19 +7601,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="27" customWidth="1" min="7" max="7"/>
-    <col width="27" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="43" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -6667,14 +7623,14 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>Table 4.7</t>
+          <t>Table 4.6</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="25" t="inlineStr">
         <is>
-          <t>Summary Descriptive Statistics: Nine-Airport Experimental Cohort Versus Top 25 Universe</t>
+          <t>The Nine-Airport Experimental Cohort Factorial Specification</t>
         </is>
       </c>
     </row>
@@ -6682,803 +7638,377 @@
     <row r="5" ht="28" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Metric Category</t>
+          <t>Airport Code</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Operational Metric</t>
+          <t>Airport Name</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Unit</t>
+          <t>Dominant Legacy Carrier</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>9-Airport Mean</t>
+          <t>Carrier Hub Role</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>9-Airport Std Dev</t>
+          <t>Dedicated Terminal Screening Complex</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>9-Airport Median</t>
+          <t>Cluster Archetype</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>9-Airport Min (Airport)</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>9-Airport Max (Airport)</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>Top 25 Mean</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>Delta (%)</t>
+          <t>Strategic Justification &amp; Selection Rationale</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>BTS OTP Operations</t>
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>BOS</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Scheduled Domestic Flights</t>
+          <t>Boston Logan</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>flights</t>
-        </is>
-      </c>
-      <c r="D6" s="26" t="n">
-        <v>224576</v>
-      </c>
-      <c r="E6" s="26" t="n">
-        <v>78441</v>
-      </c>
-      <c r="F6" s="26" t="n">
-        <v>206024</v>
+          <t>DL / AA</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Dual Focus Station</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>Terminal A (DL) &amp; Terminal B (AA)</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>Cluster 1: High-Density O&amp;D Focus</t>
+        </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>138,372 (PHL)</t>
-        </is>
-      </c>
-      <c r="H6" s="9" t="inlineStr">
-        <is>
-          <t>360,571 (ORD)</t>
-        </is>
-      </c>
-      <c r="I6" s="26" t="n">
-        <v>192160</v>
-      </c>
-      <c r="J6" s="31" t="inlineStr">
-        <is>
-          <t>+16.9%</t>
+          <t>Unconfounded Northeast high-yield O&amp;D demand; physically separate terminal finger piers.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>BTS OTP Operations</t>
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>DFW</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Cancelled Flights</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>flights</t>
-        </is>
-      </c>
-      <c r="D7" s="26" t="n">
-        <v>3623</v>
-      </c>
-      <c r="E7" s="26" t="n">
-        <v>1599</v>
-      </c>
-      <c r="F7" s="26" t="n">
-        <v>2920</v>
+          <t>Dallas/Fort Worth</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>Primary Fortress Hub</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>Terminal D Screening Complex</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>Cluster 0: Mega-Connecting Gateway</t>
+        </is>
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>1,777 (DTW)</t>
-        </is>
-      </c>
-      <c r="H7" s="9" t="inlineStr">
-        <is>
-          <t>6,515 (DFW)</t>
-        </is>
-      </c>
-      <c r="I7" s="26" t="n">
-        <v>2738</v>
-      </c>
-      <c r="J7" s="31" t="inlineStr">
-        <is>
-          <t>+32.3%</t>
+          <t>American Airlines primary mega-connecting fortress hub; high gauge international operations.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>BTS OTP Operations</t>
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>DTW</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Flight Cancellation Rate</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D8" s="31" t="inlineStr">
-        <is>
-          <t>1.63%</t>
-        </is>
-      </c>
-      <c r="E8" s="31" t="inlineStr">
-        <is>
-          <t>0.50%</t>
-        </is>
-      </c>
-      <c r="F8" s="31" t="inlineStr">
-        <is>
-          <t>1.47%</t>
+          <t>Detroit Metro</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>DL</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Primary Fortress Hub</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>McNamara Terminal Complex</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>Cluster 2: High-Reliability Fortress</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>0.99% (LAX)</t>
-        </is>
-      </c>
-      <c r="H8" s="9" t="inlineStr">
-        <is>
-          <t>2.46% (LGA)</t>
-        </is>
-      </c>
-      <c r="I8" s="31" t="inlineStr">
-        <is>
-          <t>1.43%</t>
-        </is>
-      </c>
-      <c r="J8" s="31" t="inlineStr">
-        <is>
-          <t>+14.1%</t>
+          <t>Delta primary Midwest fortress hub; world-class operational fluidity and high connecting ratio.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>BTS OTP Delays</t>
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>EWR</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Average Departure Delay</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>min</t>
-        </is>
-      </c>
-      <c r="D9" s="29" t="n">
-        <v>15.23</v>
-      </c>
-      <c r="E9" s="29" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="F9" s="29" t="n">
-        <v>15.65</v>
+          <t>Newark Liberty</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>Primary Fortress Hub</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>Terminal C Screening Complex</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>Cluster 3: Congested Coastal Originator</t>
+        </is>
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
-          <t>11.55 (DTW)</t>
-        </is>
-      </c>
-      <c r="H9" s="9" t="inlineStr">
-        <is>
-          <t>19.85 (DFW)</t>
-        </is>
-      </c>
-      <c r="I9" s="29" t="n">
-        <v>14.21</v>
-      </c>
-      <c r="J9" s="31" t="inlineStr">
-        <is>
-          <t>+7.2%</t>
+          <t>United primary East Coast fortress hub; severe New York airspace slot congestion.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>BTS OTP Delays</t>
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>IAH</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Significant Delay Rate (&gt;= 15m)</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D10" s="31" t="inlineStr">
-        <is>
-          <t>21.42%</t>
-        </is>
-      </c>
-      <c r="E10" s="31" t="inlineStr">
-        <is>
-          <t>3.30%</t>
-        </is>
-      </c>
-      <c r="F10" s="31" t="inlineStr">
-        <is>
-          <t>20.14%</t>
+          <t>Houston Bush</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>Primary Fortress Hub</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>Terminal C Screening Complex</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>Cluster 1: High-Density O&amp;D Focus</t>
         </is>
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>17.93% (LAX)</t>
-        </is>
-      </c>
-      <c r="H10" s="9" t="inlineStr">
-        <is>
-          <t>28.07% (DFW)</t>
-        </is>
-      </c>
-      <c r="I10" s="31" t="inlineStr">
-        <is>
-          <t>20.31%</t>
-        </is>
-      </c>
-      <c r="J10" s="31" t="inlineStr">
-        <is>
-          <t>+5.5%</t>
+          <t>United southern hub; balanced energy sector business O&amp;D travel and Latin American connecting banks.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>BTS OTP Delays</t>
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>LAX</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Runway Taxi-Out Queue Time</t>
+          <t>Los Angeles World</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>min</t>
-        </is>
-      </c>
-      <c r="D11" s="29" t="n">
-        <v>20.59</v>
-      </c>
-      <c r="E11" s="29" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="F11" s="29" t="n">
-        <v>20.35</v>
+          <t>DL / AA / UA</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>Tri-Carrier Parity Hub</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>Terminals 2/3 (DL), 4 (AA), 7 (UA)</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>Cluster 0: Mega-Connecting Gateway</t>
+        </is>
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>16.96 (DTW)</t>
-        </is>
-      </c>
-      <c r="H11" s="9" t="inlineStr">
-        <is>
-          <t>24.67 (EWR)</t>
-        </is>
-      </c>
-      <c r="I11" s="29" t="n">
-        <v>19.69</v>
-      </c>
-      <c r="J11" s="31" t="inlineStr">
-        <is>
-          <t>+4.5%</t>
+          <t>Massive transpacific and transcontinental origin-destination demand across all three legacy carriers.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>TSA Checkpoint</t>
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>LGA</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Total Passenger Throughput</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>pax</t>
-        </is>
-      </c>
-      <c r="D12" s="26" t="n">
-        <v>71145628</v>
-      </c>
-      <c r="E12" s="26" t="n">
-        <v>27465238</v>
-      </c>
-      <c r="F12" s="26" t="n">
-        <v>63720916</v>
+          <t>New York LaGuardia</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>DL</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>Primary Fortress Hub</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>Terminal C Screening Complex</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>Cluster 3: Congested Coastal Originator</t>
+        </is>
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>40,429,531 (PHL)</t>
-        </is>
-      </c>
-      <c r="H12" s="9" t="inlineStr">
-        <is>
-          <t>129,069,341 (LAX)</t>
-        </is>
-      </c>
-      <c r="I12" s="26" t="n">
-        <v>68495531</v>
-      </c>
-      <c r="J12" s="31" t="inlineStr">
-        <is>
-          <t>+3.9%</t>
+          <t>Consolidated Delta Terminal C (opened June 2022); perimeter rule market and pure O&amp;D flows.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>TSA Checkpoint</t>
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>ORD</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Average Daily Passenger Count</t>
+          <t>Chicago O'Hare</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>pax/day</t>
-        </is>
-      </c>
-      <c r="D13" s="26" t="n">
-        <v>53075</v>
-      </c>
-      <c r="E13" s="26" t="n">
-        <v>20473</v>
-      </c>
-      <c r="F13" s="26" t="n">
-        <v>47553</v>
+          <t>UA / AA</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>Dual Fortress Hub</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>Terminal 1 (UA) &amp; Terminal 3 (AA)</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>Cluster 0: Mega-Connecting Gateway</t>
+        </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>30,171 (PHL)</t>
-        </is>
-      </c>
-      <c r="H13" s="9" t="inlineStr">
-        <is>
-          <t>96,249 (LAX)</t>
-        </is>
-      </c>
-      <c r="I13" s="26" t="n">
-        <v>51138</v>
-      </c>
-      <c r="J13" s="31" t="inlineStr">
-        <is>
-          <t>+3.8%</t>
+          <t>Intense head-to-head legacy carrier competition; dual hub bank synchronization.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>TSA Checkpoint</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>Average Hourly Passenger Count</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>pax/hr</t>
-        </is>
-      </c>
-      <c r="D14" s="29" t="n">
-        <v>418.53</v>
-      </c>
-      <c r="E14" s="29" t="n">
-        <v>157.02</v>
-      </c>
-      <c r="F14" s="29" t="n">
-        <v>388.4</v>
-      </c>
-      <c r="G14" s="9" t="inlineStr">
-        <is>
-          <t>239.60 (ORD)</t>
-        </is>
-      </c>
-      <c r="H14" s="9" t="inlineStr">
-        <is>
-          <t>662.40 (LGA)</t>
-        </is>
-      </c>
-      <c r="I14" s="29" t="n">
-        <v>540.34</v>
-      </c>
-      <c r="J14" s="31" t="inlineStr">
-        <is>
-          <t>-22.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>TSA Checkpoint</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>Peak Single-Hour Checkpoint Rush</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>pax/hr</t>
-        </is>
-      </c>
-      <c r="D15" s="26" t="n">
-        <v>2673</v>
-      </c>
-      <c r="E15" s="26" t="n">
-        <v>881</v>
-      </c>
-      <c r="F15" s="26" t="n">
-        <v>2654</v>
-      </c>
-      <c r="G15" s="9" t="inlineStr">
-        <is>
-          <t>1,385 (DTW)</t>
-        </is>
-      </c>
-      <c r="H15" s="9" t="inlineStr">
-        <is>
-          <t>4,020 (EWR)</t>
-        </is>
-      </c>
-      <c r="I15" s="26" t="n">
-        <v>2784</v>
-      </c>
-      <c r="J15" s="31" t="inlineStr">
-        <is>
-          <t>-4.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>TSA Checkpoint</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>Demand Volatility (CV_TSA)</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="D16" s="36" t="n">
-        <v>0.8728</v>
-      </c>
-      <c r="E16" s="36" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F16" s="36" t="n">
-        <v>0.9064</v>
-      </c>
-      <c r="G16" s="9" t="inlineStr">
-        <is>
-          <t>0.6488 (BOS)</t>
-        </is>
-      </c>
-      <c r="H16" s="9" t="inlineStr">
-        <is>
-          <t>1.1240 (LGA)</t>
-        </is>
-      </c>
-      <c r="I16" s="36" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="J16" s="31" t="inlineStr">
-        <is>
-          <t>+5.8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>BTS DB1B Surveys</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>Connecting Passenger Share</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D17" s="31" t="inlineStr">
-        <is>
-          <t>47.45%</t>
-        </is>
-      </c>
-      <c r="E17" s="31" t="inlineStr">
-        <is>
-          <t>10.98%</t>
-        </is>
-      </c>
-      <c r="F17" s="31" t="inlineStr">
-        <is>
-          <t>44.41%</t>
-        </is>
-      </c>
-      <c r="G17" s="9" t="inlineStr">
-        <is>
-          <t>33.58% (EWR)</t>
-        </is>
-      </c>
-      <c r="H17" s="9" t="inlineStr">
-        <is>
-          <t>66.32% (DFW)</t>
-        </is>
-      </c>
-      <c r="I17" s="31" t="inlineStr">
-        <is>
-          <t>51.39%</t>
-        </is>
-      </c>
-      <c r="J17" s="31" t="inlineStr">
-        <is>
-          <t>-7.7%</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>BTS DB1B Surveys</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>Local Originating Passenger Share</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D18" s="31" t="inlineStr">
-        <is>
-          <t>52.55%</t>
-        </is>
-      </c>
-      <c r="E18" s="31" t="inlineStr">
-        <is>
-          <t>10.98%</t>
-        </is>
-      </c>
-      <c r="F18" s="31" t="inlineStr">
-        <is>
-          <t>55.59%</t>
-        </is>
-      </c>
-      <c r="G18" s="9" t="inlineStr">
-        <is>
-          <t>33.68% (DFW)</t>
-        </is>
-      </c>
-      <c r="H18" s="9" t="inlineStr">
-        <is>
-          <t>66.42% (EWR)</t>
-        </is>
-      </c>
-      <c r="I18" s="31" t="inlineStr">
-        <is>
-          <t>48.61%</t>
-        </is>
-      </c>
-      <c r="J18" s="31" t="inlineStr">
-        <is>
-          <t>+8.1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>BTS DB1B Surveys</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>True Local Originating TSA Demand</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>pax</t>
-        </is>
-      </c>
-      <c r="D19" s="26" t="n">
-        <v>16376561</v>
-      </c>
-      <c r="E19" s="26" t="n">
-        <v>5167458</v>
-      </c>
-      <c r="F19" s="26" t="n">
-        <v>15995278</v>
-      </c>
-      <c r="G19" s="9" t="inlineStr">
-        <is>
-          <t>10,555,299 (DTW)</t>
-        </is>
-      </c>
-      <c r="H19" s="9" t="inlineStr">
-        <is>
-          <t>26,293,897 (LAX)</t>
-        </is>
-      </c>
-      <c r="I19" s="26" t="n">
-        <v>13103484</v>
-      </c>
-      <c r="J19" s="31" t="inlineStr">
-        <is>
-          <t>+25.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>T-100 Aircraft Gauge</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>Seating Capacity per Flight</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>seats</t>
-        </is>
-      </c>
-      <c r="D20" s="29" t="n">
-        <v>168.42</v>
-      </c>
-      <c r="E20" s="29" t="n">
-        <v>7.49</v>
-      </c>
-      <c r="F20" s="29" t="n">
-        <v>168</v>
-      </c>
-      <c r="G20" s="9" t="inlineStr">
-        <is>
-          <t>154.20 (LGA)</t>
-        </is>
-      </c>
-      <c r="H20" s="9" t="inlineStr">
-        <is>
-          <t>182.30 (LAX)</t>
-        </is>
-      </c>
-      <c r="I20" s="29" t="n">
-        <v>171.1</v>
-      </c>
-      <c r="J20" s="31" t="inlineStr">
-        <is>
-          <t>-1.6%</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="13" t="inlineStr">
-        <is>
-          <t>T-100 Load Factor</t>
-        </is>
-      </c>
-      <c r="B21" s="13" t="inlineStr">
-        <is>
-          <t>Route Passenger Load Factor</t>
-        </is>
-      </c>
-      <c r="C21" s="13" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D21" s="32" t="inlineStr">
-        <is>
-          <t>85.08%</t>
-        </is>
-      </c>
-      <c r="E21" s="32" t="inlineStr">
-        <is>
-          <t>0.82%</t>
-        </is>
-      </c>
-      <c r="F21" s="32" t="inlineStr">
-        <is>
-          <t>85.26%</t>
-        </is>
-      </c>
-      <c r="G21" s="13" t="inlineStr">
-        <is>
-          <t>83.85% (DTW)</t>
-        </is>
-      </c>
-      <c r="H21" s="13" t="inlineStr">
-        <is>
-          <t>86.12% (EWR)</t>
-        </is>
-      </c>
-      <c r="I21" s="32" t="inlineStr">
-        <is>
-          <t>84.73%</t>
-        </is>
-      </c>
-      <c r="J21" s="32" t="inlineStr">
-        <is>
-          <t>+0.4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="28" t="inlineStr">
-        <is>
-          <t>Note. Formal Welch's two-sample t-tests demonstrating no statistically significant differences between the 9-airport experimental cohort and the Top 25 airport universe across operational metrics (all p &gt; 0.05).</t>
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>PHL</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>Philadelphia Intl</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>Primary Fortress Hub</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>Terminals B &amp; C Complexes</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t>Cluster 2: High-Reliability Fortress</t>
+        </is>
+      </c>
+      <c r="G14" s="13" t="inlineStr">
+        <is>
+          <t>American Mid-Atlantic transatlantic hub; counterpart to Delta's Midwestern fortress at DTW.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="28" t="inlineStr">
+        <is>
+          <t>Note. Balanced 4x4 factorial specification establishing the 9-airport experimental cohort across 12 carrier-exclusive complexes, controlling for physical checkpoint topology and hub banking structure.</t>
         </is>
       </c>
     </row>
